--- a/暫定案.xlsx
+++ b/暫定案.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>BSW</t>
     <phoneticPr fontId="1"/>
@@ -40,6 +40,10 @@
     <rPh sb="19" eb="20">
       <t>アン</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>あ</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -116,6 +120,12 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFFCCFF"/>
+      <color rgb="FFCC99FF"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -131,16 +141,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>666751</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>8002</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>27214</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>163286</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>762001</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>9526</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -149,8 +159,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6381751" y="1600038"/>
-          <a:ext cx="5891892" cy="5815855"/>
+          <a:off x="6496050" y="342900"/>
+          <a:ext cx="4791076" cy="352426"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -205,16 +215,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>199305</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>770799</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>52828</xdr:rowOff>
+      <xdr:rowOff>12748</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>501864</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>40822</xdr:rowOff>
+      <xdr:colOff>266535</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>133349</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -223,8 +233,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6730734" y="1998649"/>
-          <a:ext cx="5201130" cy="1226244"/>
+          <a:off x="6418564" y="1861719"/>
+          <a:ext cx="5143500" cy="1633395"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -557,15 +567,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>199305</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>134472</xdr:rowOff>
+      <xdr:colOff>721</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>18811</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>501864</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>22413</xdr:rowOff>
+      <xdr:colOff>299117</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>67236</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -574,8 +584,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6730734" y="3318543"/>
-          <a:ext cx="5201130" cy="1303084"/>
+          <a:off x="6455309" y="3716752"/>
+          <a:ext cx="5139337" cy="2401660"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -636,7 +646,7 @@
               <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>u1g_bbsw2iosif_vel       </a:t>
+            <a:t>u2g_bbsw2iosif_vel        </a:t>
           </a:r>
           <a:r>
             <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
@@ -662,6 +672,72 @@
             </a:rPr>
             <a:t>0 - 300[km/h]</a:t>
           </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>u2g_bbsw2iosif_rpm</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" baseline="0">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>        </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" baseline="0">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>仮想マシン回転数 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" baseline="0">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>0 - 10000[rpm]</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>u2g_bbsw2iosif_gear</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" baseline="0">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>       </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" baseline="0">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>仮想マシンギア状態 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" baseline="0">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>1,2,3,4,5,6,N[-]</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" baseline="0">
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
         </a:p>
         <a:p>
           <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
@@ -676,15 +752,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>201705</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>44026</xdr:rowOff>
+      <xdr:colOff>70810</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>29830</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>504264</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>163286</xdr:rowOff>
+      <xdr:colOff>373369</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>50426</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -693,8 +769,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6733134" y="4643240"/>
-          <a:ext cx="5201130" cy="826832"/>
+          <a:off x="6525398" y="6417183"/>
+          <a:ext cx="5143500" cy="1197214"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -873,15 +949,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>188099</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>60032</xdr:rowOff>
+      <xdr:colOff>39450</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>75745</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>490658</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>27215</xdr:rowOff>
+      <xdr:colOff>337137</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>117101</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -890,8 +966,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6719528" y="5543711"/>
-          <a:ext cx="5201130" cy="1028540"/>
+          <a:off x="6494038" y="7807804"/>
+          <a:ext cx="5138628" cy="1386062"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1197,15 +1273,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>190500</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>149681</xdr:rowOff>
+      <xdr:colOff>31009</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>125148</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>493059</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>122465</xdr:rowOff>
+      <xdr:colOff>330766</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>161363</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1214,8 +1290,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6721929" y="6694717"/>
-          <a:ext cx="5201130" cy="503462"/>
+          <a:off x="6485597" y="9370001"/>
+          <a:ext cx="5140698" cy="708568"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1307,15 +1383,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>258536</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>13607</xdr:rowOff>
+      <xdr:colOff>182334</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>161926</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>26</xdr:col>
-      <xdr:colOff>598714</xdr:colOff>
-      <xdr:row>55</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>800100</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>142876</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1324,8 +1400,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13321393" y="1605643"/>
-          <a:ext cx="8504464" cy="8218714"/>
+          <a:off x="13136334" y="333376"/>
+          <a:ext cx="6285141" cy="323850"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1367,7 +1443,7 @@
               <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
               <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
             </a:rPr>
-            <a:t>BSW</a:t>
+            <a:t>SAC</a:t>
           </a:r>
           <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
             <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
@@ -1383,13 +1459,13 @@
       <xdr:col>16</xdr:col>
       <xdr:colOff>607519</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>58433</xdr:rowOff>
+      <xdr:rowOff>58434</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>23</xdr:col>
-      <xdr:colOff>93649</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>46427</xdr:rowOff>
+      <xdr:colOff>100853</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>78441</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1398,8 +1474,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13670376" y="2004254"/>
-          <a:ext cx="5201130" cy="1226244"/>
+          <a:off x="13516695" y="1907405"/>
+          <a:ext cx="5141099" cy="1532801"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1436,6 +1512,149 @@
         <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
         <a:lstStyle/>
         <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>sacelcrtif.h</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>vdg_sacelcrtif_pwon()</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" baseline="0">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>   </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" baseline="0">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>アクセルスロットル補正初期化処理関数</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" baseline="0">
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>vdg_sacelcrtif_4msm()   </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>アクセルスロットル補正定期処理関数</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>u1g_sacelcrtif_thlpct   </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>補正アクセルスロットル開度</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>0-100[%]</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>u1g_sacelcrtif_crtflg   </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>アクセルスロットル補正有無 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>OFF,ON[-]</a:t>
+          </a:r>
           <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
             <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
             <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
@@ -1448,15 +1667,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>607519</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>140077</xdr:rowOff>
+      <xdr:colOff>715576</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>119536</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>23</xdr:col>
-      <xdr:colOff>93649</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>28018</xdr:rowOff>
+      <xdr:colOff>201706</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>65636</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1465,8 +1684,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13670376" y="3324148"/>
-          <a:ext cx="5201130" cy="1303084"/>
+          <a:off x="13624752" y="3649389"/>
+          <a:ext cx="5133895" cy="1626982"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1503,9 +1722,149 @@
         <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
         <a:lstStyle/>
         <a:p>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
-            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
-            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>sbrkcrtif.h</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>vdg_sbrkcrtif_pwon()    </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>ブレーキペダル補正初期化処理関数</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>vdg_sbrkcrtif_4msm()    </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>ブレーキペダル補正定期処理関数</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>u1g_sbrkcrtif_pdlpct    </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>補正ブレーキペダル開度 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>0-100[%]</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>u1g_sbrkcrtif_crtflg    </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>ブレーキペダル補正有無 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>OFF,ON[-]</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
+            <a:effectLst/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -1515,15 +1874,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>609919</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>49631</xdr:rowOff>
+      <xdr:colOff>528276</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>39046</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>23</xdr:col>
-      <xdr:colOff>96049</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>168891</xdr:rowOff>
+      <xdr:colOff>14406</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1532,8 +1891,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13672776" y="4648845"/>
-          <a:ext cx="5201130" cy="826832"/>
+          <a:off x="13591133" y="5699617"/>
+          <a:ext cx="5201130" cy="1552990"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1570,6 +1929,44 @@
         <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
         <a:lstStyle/>
         <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>sclthcrtif.h</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>vdg_sclthcrtif_pwon()   </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>クラッチペダル補正初期化処理関数</a:t>
+          </a:r>
           <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:schemeClr val="dk1"/>
@@ -1579,6 +1976,117 @@
             <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
             <a:cs typeface="+mn-cs"/>
           </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>vdg_sclthcrtif_16msm()  </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>クラッチペダル補正定期処理関数</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>u1g_sclthcrtif_pdlpct   </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>補正クラッチペダル開度 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>0-100[%]</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>u1g_sclthcrtif_crtflg   </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>クラッチペダル補正有無 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>OFF,ON[-]</a:t>
+          </a:r>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -1587,15 +2095,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>596313</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>65637</xdr:rowOff>
+      <xdr:colOff>690818</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>115085</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>23</xdr:col>
-      <xdr:colOff>82443</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>32820</xdr:rowOff>
+      <xdr:colOff>176948</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>45622</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1604,8 +2112,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13659170" y="5549316"/>
-          <a:ext cx="5201130" cy="1028540"/>
+          <a:off x="13753675" y="7544585"/>
+          <a:ext cx="5201130" cy="1345680"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1642,6 +2150,126 @@
         <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
         <a:lstStyle/>
         <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>sigswcrtif.h</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>vdg_sigswcrtif_pwon()   </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>イグニッションスイッチ補正初期化処理関数</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" baseline="0">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>vdg_sigswcrtif_16msm()  </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>イグニッションスイッチ補正定期処理関数</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" baseline="0">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>u1g_sigsw_sts           </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>イグニッションスイッチステータス </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>OFF,ON[-]</a:t>
+          </a:r>
           <a:endParaRPr lang="ja-JP" altLang="ja-JP" sz="1100" b="0" i="0" baseline="0">
             <a:solidFill>
               <a:schemeClr val="dk1"/>
@@ -1659,15 +2287,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>598714</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>155286</xdr:rowOff>
+      <xdr:colOff>708302</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>6340</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>23</xdr:col>
-      <xdr:colOff>84844</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>128070</xdr:rowOff>
+      <xdr:colOff>194432</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>121662</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1676,8 +2304,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13661571" y="6700322"/>
-          <a:ext cx="5201130" cy="503462"/>
+          <a:off x="13771159" y="9027876"/>
+          <a:ext cx="5201130" cy="1530465"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1714,6 +2342,44 @@
         <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
         <a:lstStyle/>
         <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>sgearcrtif.h</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>vdg_sgearcrtif_pwon()   </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>ギアポジション補正初期化処理関数</a:t>
+          </a:r>
           <a:endParaRPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:schemeClr val="dk1"/>
@@ -1724,8 +2390,3452 @@
             <a:cs typeface="+mn-cs"/>
           </a:endParaRPr>
         </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>vdg_sgearcrtif_16msm()</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>　ギアポジション補正定期処理関数</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>s1g_sgearcrtif_pos      </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>補正ギアポジション情報 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>1,2,3,4,5,6,N[-]</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>u1g_sgearcrtif_crtflg   </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>ギアポジション補正有無 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>OFF,ON[-]</a:t>
+          </a:r>
+        </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>712536</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>59942</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>198666</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>88047</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="18" name="テキスト ボックス 17"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13775393" y="10673513"/>
+          <a:ext cx="5201130" cy="1443248"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent4">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>avelif.h</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>vdg_avelif_pwon()       </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>確定演算マシン速度初期化処理関数</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>vdg_avelif_16msm()      </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>確定演算マシン速度定期処理関数</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>u2g_avelif_spd          </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>確定演算マシン速度 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>0 - 300[km/h]</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>653942</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>116065</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>136934</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>166487</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="19" name="テキスト ボックス 18"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13716799" y="13736815"/>
+          <a:ext cx="5197992" cy="1465565"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent4">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>agearcfmif.h</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>vdg_sgearcfmif_pwon()   </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>確定演算ギア状態初期化処理関数</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>vdg_sgearcfmif_16msm()  </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>確定演算ギア状態定期処理関数</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>s1g_sgearcfmif_pos      </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>確定演算ギア状態 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>1,2,3,4,5,6,N[-]</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>709442</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>3652</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>195572</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>23211</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="20" name="テキスト ボックス 19"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13772299" y="12209259"/>
+          <a:ext cx="5201130" cy="1434702"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent4">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>arpmcfmif.h</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>vdg_arpmcfmif_pwon()    </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>確定演算マシン回転数初期化処理関数</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>vdg_arpmcfmif_16msm()   </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>確定演算マシン回転数定期処理関数</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>u2g_arpmcfmif_val       </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>確定演算マシン回転数 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>0 - 10000[rpm]</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>292474</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>82363</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>657393</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="22" name="テキスト ボックス 21"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="20533099" y="253813"/>
+          <a:ext cx="6032294" cy="441512"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>APL</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>41</xdr:col>
+      <xdr:colOff>460169</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="23" name="テキスト ボックス 22"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="27622500" y="323850"/>
+          <a:ext cx="6032294" cy="323850"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="CC99FF"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>SAC</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>683559</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>11204</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>176893</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>108857</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="24" name="テキスト ボックス 23"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="21094273" y="1957025"/>
+          <a:ext cx="5208334" cy="1335903"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>ppermif.h</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>vdg_ppermif_pwon()       </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>許可調停管理初期化処理関数</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>vdg_ppermif_4msm()       </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>許可調停管理定期処理関数</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>u1g_ppermif_eng          </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>仮想エンジン許可調停結果 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>OFF,ON[-]</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>u1g_ppermif_sht          </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>仮想シフト遷移調停結果 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>OFF,ON[-]</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>66324</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>35106</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>376087</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>136070</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="25" name="テキスト ボックス 24"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="21293467" y="3749856"/>
+          <a:ext cx="5208334" cy="1869893"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>pprtctif.h</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>vdg_pprtctif_pwon()</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" baseline="0">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>      </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" baseline="0">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>保護調停管理初期化処理関数</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>vdg_pprtctif_4msm()      </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>保護調停管理定期処理関数</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>u1g_pprtctif_ovrvsts     </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>オーバーレブ調停管理結果 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>OFF,ON[-] </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>u1g_pprtctif_clthszsts   </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>クラッチ焼き付き調停管理結果 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>OFF,ON[-]</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>u1g_pprtctif_brkszsts    </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>ブレーキ焼き付き調停管理結果 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>OFF,ON[-]</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>u1g_pprtctif_enststs     </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>エンジンストール調停管理結果 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>OFF,ON[-] </a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>58147</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>123469</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>367910</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>40822</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="26" name="テキスト ボックス 25"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="21285290" y="5784040"/>
+          <a:ext cx="5208334" cy="1332496"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>pwarnif.h</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>vdg_pwarnif_pwon()</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" baseline="0">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>       </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" baseline="0">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>警告通知初期化処理関数</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>vdg_pwarnif_64msm()      </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>警告通知定期処理関数</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>u1g_pwarnif_ovrhet       </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>オーバーヒート状態警告 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>OFF,ON[-]</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>u1g_pwarnif_snserr       </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>センサー状態警告 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>OFF,ON[-]</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>815666</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>86969</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>309000</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>54429</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="27" name="テキスト ボックス 26"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="21226380" y="7339576"/>
+          <a:ext cx="5208334" cy="2443960"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>psimbrdgif.h</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>vdg_psimbrdgif_pwon()</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" baseline="0">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>     仮想想演算ブリッジ初期化処理関数</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>vdg_psimbrdgif_4msm()</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>　   仮想演算ブリッジ定期処理関数</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>u1g_psimbrdgif_aclthlpct  </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>仮想演算用アクセルスロットル開度</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>u1g_psimbrdgif_brkpdlpct  </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>仮想演算用ブレーキペダル開度</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>u1g_psimbrdgif_clthpdlpct </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>仮想演算用クラッチペダル開度</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>  </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>s1g_psimbrdgif_gearpos    </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>仮想演算用ギア状態</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>u2g_psimbrdgif_velspd     </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>仮想演算用速度</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>u2g_psimbrdgif_rpmval     </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>仮想演算用回転数</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>s1g_psimbrdgif_gearcfmpos </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>仮想演算用確定ギア状態</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>773932</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>171089</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>267266</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>9847</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="28" name="テキスト ボックス 27"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="21184646" y="13438053"/>
+          <a:ext cx="5208334" cy="1077008"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>2522</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>161864</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>312285</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>108857</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="29" name="テキスト ボックス 28"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="21229665" y="9890971"/>
+          <a:ext cx="5208334" cy="2069707"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>pvehstsif.h</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>vdg_pvehstsif_pwon()    </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>仮想マシン状態初期化処理関数</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>vdg_pvehstsif_64msm()</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" baseline="0">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>   </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" baseline="0">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>仮想マシン状態定期処理関数</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>u1g_pvehstsif_stop      </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>仮想マシン停止状態</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>u1g_pvehstsif_run       </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>仮想マシン走行状態</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>u1g_pvehstsif_spdup     </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>仮想マシン加速状態</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>u1g_pvehstsif_spddw     </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>仮想マシン減速状態</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>u1g_pvehstsif_enst      </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>仮想マシンエンジンストール状態</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>765214</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>72664</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>258548</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>88313</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="30" name="テキスト ボックス 29"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="21175928" y="12278271"/>
+          <a:ext cx="5208334" cy="1077006"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>217715</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>56830</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>40</xdr:col>
+      <xdr:colOff>527477</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>154483</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="31" name="テキスト ボックス 30"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="27976286" y="2179544"/>
+          <a:ext cx="5208334" cy="1335903"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFCCFF"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr rtl="0" eaLnBrk="0" fontAlgn="base" hangingPunct="0"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>mengif.h</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr rtl="0" eaLnBrk="0" fontAlgn="base" hangingPunct="0"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>vdg_mengif_pwon()</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr rtl="0" eaLnBrk="0" fontAlgn="base" hangingPunct="0"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>vdg_mengif_4msm()</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr rtl="0" eaLnBrk="0" fontAlgn="base" hangingPunct="0"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>u1g_mengif_trq</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr rtl="0" eaLnBrk="0" fontAlgn="base" hangingPunct="0"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>u1g_mengif_rpm</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>296636</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>141194</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>40</xdr:col>
+      <xdr:colOff>606398</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>67397</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="32" name="テキスト ボックス 31"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="27823886" y="3570194"/>
+          <a:ext cx="5167512" cy="1297803"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFCCFF"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr rtl="0" eaLnBrk="0" fontAlgn="base" hangingPunct="0"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>mclthif.h</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr rtl="0" eaLnBrk="0" fontAlgn="base" hangingPunct="0"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>vdg_mclthif_pwon()</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr rtl="0" eaLnBrk="0" fontAlgn="base" hangingPunct="0"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>vdg_mclthif_4msm()</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr rtl="0" eaLnBrk="0" fontAlgn="base" hangingPunct="0"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>u1g_mclthif_transtrq</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr rtl="0" eaLnBrk="0" fontAlgn="base" hangingPunct="0"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>u1g_mclthif_amtslip</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr rtl="0" eaLnBrk="0" fontAlgn="base" hangingPunct="0"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>u1g_mclthif_temp</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>382361</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>93569</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>40</xdr:col>
+      <xdr:colOff>692123</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>19772</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="33" name="テキスト ボックス 32"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="27909611" y="5065619"/>
+          <a:ext cx="5167512" cy="1297803"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFCCFF"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr rtl="0" eaLnBrk="0" fontAlgn="base" hangingPunct="0"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>mgearboxif.h</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr rtl="0" eaLnBrk="0" fontAlgn="base" hangingPunct="0"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>vdg_mgearboxif_pwon()</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr rtl="0" eaLnBrk="0" fontAlgn="base" hangingPunct="0"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>vdg_mgearboxif_4msm()</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr rtl="0" eaLnBrk="0" fontAlgn="base" hangingPunct="0"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>u1g_mgearboxif_outtrq</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr rtl="0" eaLnBrk="0" fontAlgn="base" hangingPunct="0"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>u1g_mgearboxif_gearrto</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>382361</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>17369</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>40</xdr:col>
+      <xdr:colOff>692123</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>115022</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="34" name="テキスト ボックス 33"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="27909611" y="6532469"/>
+          <a:ext cx="5167512" cy="1297803"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFCCFF"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr rtl="0" eaLnBrk="0" fontAlgn="base" hangingPunct="0"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>mvirtmachif.h</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr rtl="0" eaLnBrk="0" fontAlgn="base" hangingPunct="0"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>vdg_mvirtmachif_pwon()</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr rtl="0" eaLnBrk="0" fontAlgn="base" hangingPunct="0"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>vdg_mvirtmachif_4msm()</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>　</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr rtl="0" eaLnBrk="0" fontAlgn="base" hangingPunct="0"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>u1g_mvirtmachif_speed</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr rtl="0" eaLnBrk="0" fontAlgn="base" hangingPunct="0"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>u1g_mvirtmachif_acelratn</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr rtl="0" eaLnBrk="0" fontAlgn="base" hangingPunct="0"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>u1g_mvirtmachif_trvldist</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>429986</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>93569</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>40</xdr:col>
+      <xdr:colOff>739748</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>19772</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="35" name="テキスト ボックス 34"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="27957236" y="8151719"/>
+          <a:ext cx="5167512" cy="1297803"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFCCFF"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr rtl="0" eaLnBrk="0" fontAlgn="base" hangingPunct="0"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>mbrakeif.h</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr rtl="0" eaLnBrk="0" fontAlgn="base" hangingPunct="0"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>vdg_mbrakeif_pwon()</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr rtl="0" eaLnBrk="0" fontAlgn="base" hangingPunct="0"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>vdg_mbrakeif_4msm()</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>　</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr rtl="0" eaLnBrk="0" fontAlgn="base" hangingPunct="0"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>u1g_mbrakeif_force</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr rtl="0" eaLnBrk="0" fontAlgn="base" hangingPunct="0"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>u1g_mbrakeif_temp</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>266535</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>152482</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>607519</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>157093</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="3" name="カギ線コネクタ 2"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="4" idx="3"/>
+          <a:endCxn id="13" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="11562064" y="2673806"/>
+          <a:ext cx="1954631" cy="4611"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 50000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>266535</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>159370</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>715576</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>92586</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="36" name="カギ線コネクタ 35"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="4" idx="3"/>
+          <a:endCxn id="14" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11601285" y="2748979"/>
+          <a:ext cx="2068291" cy="1832263"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 76077"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>266535</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>157309</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>528276</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>103783</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="42" name="カギ線コネクタ 41"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="4" idx="3"/>
+          <a:endCxn id="15" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11652573" y="2685097"/>
+          <a:ext cx="1888318" cy="3485378"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 76889"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>266535</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>157309</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>690818</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>80354</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="45" name="カギ線コネクタ 44"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="4" idx="3"/>
+          <a:endCxn id="16" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11652573" y="2685097"/>
+          <a:ext cx="2050860" cy="5147142"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 63197"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>266535</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>157309</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>708302</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>64001</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="49" name="カギ線コネクタ 48"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="4" idx="3"/>
+          <a:endCxn id="17" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11652573" y="2685097"/>
+          <a:ext cx="2068344" cy="6647462"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 55452"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>299117</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>43023</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>712536</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>73995</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="52" name="カギ線コネクタ 51"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="18" idx="1"/>
+          <a:endCxn id="7" idx="3"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="10800000">
+          <a:off x="11594646" y="4917582"/>
+          <a:ext cx="2027066" cy="5914060"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 50000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>299117</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>43024</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>709442</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>13433</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="59" name="カギ線コネクタ 58"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="20" idx="1"/>
+          <a:endCxn id="7" idx="3"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="10800000">
+          <a:off x="11594646" y="4917583"/>
+          <a:ext cx="2023972" cy="7366291"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 50000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>299117</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>43024</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>653942</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>141277</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="62" name="カギ線コネクタ 61"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="19" idx="1"/>
+          <a:endCxn id="7" idx="3"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="10800000">
+          <a:off x="11594646" y="4917583"/>
+          <a:ext cx="1968472" cy="8838841"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 55123"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>194432</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>144075</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>683559</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>64001</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="78" name="カギ線コネクタ 77"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="17" idx="3"/>
+          <a:endCxn id="24" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="18751373" y="2497310"/>
+          <a:ext cx="2102774" cy="6811544"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 50000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>176948</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>144075</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>683559</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>80354</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="81" name="カギ線コネクタ 80"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="16" idx="3"/>
+          <a:endCxn id="24" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="18733889" y="2497310"/>
+          <a:ext cx="2120258" cy="5315103"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 43129"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>201706</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>85589</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>66324</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>92587</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="85" name="カギ線コネクタ 84"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="14" idx="3"/>
+          <a:endCxn id="25" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="18979563" y="4684803"/>
+          <a:ext cx="2313904" cy="6998"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 50000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>166806</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>85589</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>66324</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>83477</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="89" name="カギ線コネクタ 88"/>
+        <xdr:cNvCxnSpPr>
+          <a:endCxn id="25" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="18944663" y="4684803"/>
+          <a:ext cx="2348804" cy="1943710"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 92953"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -1994,13 +6104,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="F1:J10"/>
+  <dimension ref="F1:AS12"/>
   <sheetFormatPr defaultColWidth="10.625" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="16384" width="10.625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="6:10" x14ac:dyDescent="0.15">
+    <row r="1" spans="6:45" x14ac:dyDescent="0.15">
       <c r="F1" s="2" t="s">
         <v>1</v>
       </c>
@@ -2009,16 +6119,21 @@
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
     </row>
-    <row r="2" spans="6:10" x14ac:dyDescent="0.15">
+    <row r="2" spans="6:45" x14ac:dyDescent="0.15">
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
     </row>
-    <row r="10" spans="6:10" x14ac:dyDescent="0.15">
+    <row r="10" spans="6:45" x14ac:dyDescent="0.15">
       <c r="H10" s="1" t="s">
         <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="6:45" x14ac:dyDescent="0.15">
+      <c r="AS12" s="1" t="s">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/暫定案.xlsx
+++ b/暫定案.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="153222"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\share\zun-sim\"/>
@@ -215,16 +215,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>770799</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>12748</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>517</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>167753</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>266535</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>133349</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>805962</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>152047</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -233,8 +233,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6418564" y="1861719"/>
-          <a:ext cx="5143500" cy="1633395"/>
+          <a:off x="6531946" y="1759789"/>
+          <a:ext cx="4887587" cy="1222544"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -302,7 +302,7 @@
               <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
               <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
             </a:rPr>
-            <a:t>   </a:t>
+            <a:t> </a:t>
           </a:r>
           <a:r>
             <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
@@ -358,6 +358,118 @@
               <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
               <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
             </a:rPr>
+            <a:t>  </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>ブレーキペダル開度    </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>0-100[%]</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ja-JP">
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>u1g_bios2bswif_clthpdl</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>クラッチペダル開度   </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>0-100[%]</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ja-JP">
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>u1g_bios2bswif_gear</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
             <a:t>    </a:t>
           </a:r>
           <a:r>
@@ -370,7 +482,7 @@
               <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>ブレーキペダル開度    </a:t>
+            <a:t>ギア情報    </a:t>
           </a:r>
           <a:r>
             <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
@@ -382,19 +494,15 @@
               <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>0-100[%]</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ja-JP" altLang="en-US">
+            <a:t>1,2,3,4,5,6,N[-]</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP">
               <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
               <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-US" altLang="ja-JP">
-            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
-            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
-          </a:endParaRPr>
         </a:p>
         <a:p>
           <a:r>
@@ -407,14 +515,14 @@
               <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>u1g_bios2bswif_clthpdl</a:t>
+            <a:t>u1g_bios2bswif_igsw</a:t>
           </a:r>
           <a:r>
             <a:rPr lang="en-US" altLang="ja-JP">
               <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
               <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
             </a:rPr>
-            <a:t>   </a:t>
+            <a:t>    </a:t>
           </a:r>
           <a:r>
             <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
@@ -426,7 +534,7 @@
               <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>クラッチペダル開度   </a:t>
+            <a:t>イグニッションスイッチステータ</a:t>
           </a:r>
           <a:r>
             <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
@@ -438,115 +546,7 @@
               <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>0-100[%]</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ja-JP" altLang="en-US">
-              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
-              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" altLang="ja-JP">
-            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
-            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
-              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>u1g_bios2bswif_gear</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ja-JP">
-              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
-              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
-            </a:rPr>
-            <a:t>      </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
-              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>ギア情報    </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
-              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>1,2,3,4,5,6,N[-]</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ja-JP">
-              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
-              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
-              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>u1g_bios2bswif_igsw</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ja-JP">
-              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
-              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
-            </a:rPr>
-            <a:t>      </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
-              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>イグニッションスイッチステータ</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
-              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>0(off),1(on)[-]</a:t>
+            <a:t>OFF,ON[-]</a:t>
           </a:r>
           <a:r>
             <a:rPr lang="en-US" altLang="ja-JP">
@@ -567,15 +567,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>721</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>18811</xdr:rowOff>
+      <xdr:colOff>9003</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>173814</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>299117</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>67236</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>805962</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>168702</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -584,8 +584,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6455309" y="3716752"/>
-          <a:ext cx="5139337" cy="2401660"/>
+          <a:off x="6540432" y="3357885"/>
+          <a:ext cx="4879101" cy="879353"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -752,15 +752,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>70810</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>29830</xdr:rowOff>
+      <xdr:colOff>4550</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>168272</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>373369</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>50426</xdr:rowOff>
+      <xdr:colOff>7328</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>152047</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -769,8 +769,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6525398" y="6417183"/>
-          <a:ext cx="5143500" cy="1197214"/>
+          <a:off x="6535979" y="4590593"/>
+          <a:ext cx="4901349" cy="868240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -948,16 +948,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>39450</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>75745</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>809734</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>164488</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>337137</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>117101</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>805963</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>152046</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -966,8 +966,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6494038" y="7807804"/>
-          <a:ext cx="5138628" cy="1386062"/>
+          <a:off x="6524734" y="5825059"/>
+          <a:ext cx="4894800" cy="1048916"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1272,16 +1272,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>31009</xdr:colOff>
-      <xdr:row>55</xdr:row>
-      <xdr:rowOff>125148</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>809575</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>164195</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>330766</xdr:colOff>
-      <xdr:row>59</xdr:row>
-      <xdr:rowOff>161363</xdr:rowOff>
+      <xdr:colOff>7328</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>167409</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1290,8 +1290,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6485597" y="9370001"/>
-          <a:ext cx="5140698" cy="708568"/>
+          <a:off x="6524575" y="7063016"/>
+          <a:ext cx="4912753" cy="533893"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1456,16 +1456,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>607519</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>58434</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>4047</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>8479</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>23</xdr:col>
-      <xdr:colOff>100853</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>78441</xdr:rowOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>8282</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1474,8 +1474,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13516695" y="1907405"/>
-          <a:ext cx="5141099" cy="1532801"/>
+          <a:off x="13802873" y="1747827"/>
+          <a:ext cx="4866127" cy="1043412"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1666,16 +1666,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>715576</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>119536</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>1202</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>2305</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>23</xdr:col>
-      <xdr:colOff>201706</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>65636</xdr:rowOff>
+      <xdr:colOff>9526</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1684,8 +1684,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13624752" y="3649389"/>
-          <a:ext cx="5133895" cy="1626982"/>
+          <a:off x="13764827" y="3088405"/>
+          <a:ext cx="4866074" cy="1026395"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1873,16 +1873,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>528276</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>39046</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>8064</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>9738</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>23</xdr:col>
-      <xdr:colOff>14406</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>9526</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>161192</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1891,8 +1891,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13591133" y="5699617"/>
-          <a:ext cx="5201130" cy="1552990"/>
+          <a:off x="13771689" y="4467438"/>
+          <a:ext cx="4859212" cy="1008704"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2094,16 +2094,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>690818</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>115085</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>2087</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>5182</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>23</xdr:col>
-      <xdr:colOff>176948</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>45622</xdr:rowOff>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2112,8 +2112,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13753675" y="7544585"/>
-          <a:ext cx="5201130" cy="1345680"/>
+          <a:off x="13765712" y="5834482"/>
+          <a:ext cx="4855664" cy="852068"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2286,16 +2286,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>708302</xdr:colOff>
-      <xdr:row>51</xdr:row>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>1254</xdr:colOff>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>6340</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>23</xdr:col>
-      <xdr:colOff>194432</xdr:colOff>
-      <xdr:row>59</xdr:row>
-      <xdr:rowOff>121662</xdr:rowOff>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>161192</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2304,8 +2304,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13771159" y="9027876"/>
-          <a:ext cx="5201130" cy="1530465"/>
+          <a:off x="13764879" y="7035790"/>
+          <a:ext cx="4866021" cy="1012102"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2498,16 +2498,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>712536</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>59942</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>1825</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>1326</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>23</xdr:col>
-      <xdr:colOff>198666</xdr:colOff>
-      <xdr:row>68</xdr:row>
-      <xdr:rowOff>88047</xdr:rowOff>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>168518</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2516,8 +2516,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13775393" y="10673513"/>
-          <a:ext cx="5201130" cy="1443248"/>
+          <a:off x="13765450" y="8402376"/>
+          <a:ext cx="4855926" cy="852992"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2684,16 +2684,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>653942</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>116065</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>182</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>168021</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>23</xdr:col>
-      <xdr:colOff>136934</xdr:colOff>
-      <xdr:row>85</xdr:row>
-      <xdr:rowOff>166487</xdr:rowOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2702,8 +2702,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13716799" y="13736815"/>
-          <a:ext cx="5197992" cy="1465565"/>
+          <a:off x="13763807" y="10797921"/>
+          <a:ext cx="4857568" cy="860680"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2867,16 +2867,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>709442</xdr:colOff>
-      <xdr:row>69</xdr:row>
-      <xdr:rowOff>3652</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>8057</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>23</xdr:col>
-      <xdr:colOff>195572</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>23211</xdr:rowOff>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>7327</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2885,8 +2885,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13772299" y="12209259"/>
-          <a:ext cx="5201130" cy="1434702"/>
+          <a:off x="13771682" y="9601200"/>
+          <a:ext cx="4859218" cy="864577"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3182,7 +3182,7 @@
               <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
               <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
             </a:rPr>
-            <a:t>SAC</a:t>
+            <a:t>SIM</a:t>
           </a:r>
           <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
             <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
@@ -3196,15 +3196,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>25</xdr:col>
-      <xdr:colOff>683559</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>11204</xdr:rowOff>
+      <xdr:colOff>801221</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>11203</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>32</xdr:col>
-      <xdr:colOff>176893</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>108857</xdr:rowOff>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>795618</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3213,8 +3213,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="21094273" y="1957025"/>
-          <a:ext cx="5208334" cy="1335903"/>
+          <a:off x="20971809" y="1692085"/>
+          <a:ext cx="4835338" cy="997327"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3356,15 +3356,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>26</xdr:col>
-      <xdr:colOff>66324</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>35106</xdr:rowOff>
+      <xdr:colOff>8253</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>12695</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>32</xdr:col>
-      <xdr:colOff>376087</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>136070</xdr:rowOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3373,8 +3373,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="21293467" y="3749856"/>
-          <a:ext cx="5208334" cy="1869893"/>
+          <a:off x="20985665" y="3038283"/>
+          <a:ext cx="4832688" cy="1500099"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3569,15 +3569,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>26</xdr:col>
-      <xdr:colOff>58147</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>123469</xdr:rowOff>
+      <xdr:colOff>13324</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>205</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>32</xdr:col>
-      <xdr:colOff>367910</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>40822</xdr:rowOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3586,8 +3586,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="21285290" y="5784040"/>
-          <a:ext cx="5208334" cy="1332496"/>
+          <a:off x="20990736" y="4874764"/>
+          <a:ext cx="4827617" cy="1008324"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3732,15 +3732,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>25</xdr:col>
-      <xdr:colOff>815666</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>86969</xdr:rowOff>
+      <xdr:colOff>803740</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>163115</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>32</xdr:col>
-      <xdr:colOff>309000</xdr:colOff>
-      <xdr:row>55</xdr:row>
-      <xdr:rowOff>54429</xdr:rowOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>156884</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3749,8 +3749,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="21226380" y="7339576"/>
-          <a:ext cx="5208334" cy="2443960"/>
+          <a:off x="20974328" y="6214291"/>
+          <a:ext cx="4844025" cy="2010828"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4054,15 +4054,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>26</xdr:col>
-      <xdr:colOff>2522</xdr:colOff>
-      <xdr:row>55</xdr:row>
-      <xdr:rowOff>161864</xdr:rowOff>
+      <xdr:colOff>13728</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>4982</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>32</xdr:col>
-      <xdr:colOff>312285</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>108857</xdr:rowOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>156882</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4071,8 +4071,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="21229665" y="9890971"/>
-          <a:ext cx="5208334" cy="2069707"/>
+          <a:off x="20991140" y="8577482"/>
+          <a:ext cx="4827213" cy="1664694"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4114,7 +4114,7 @@
               <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
               <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
             </a:rPr>
-            <a:t>pvehstsif.h</a:t>
+            <a:t>pvehstsjdgif.h</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -4123,14 +4123,14 @@
               <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
               <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
             </a:rPr>
-            <a:t>vdg_pvehstsif_pwon()    </a:t>
+            <a:t>vdg_pvehstsjdgif_pwon()    </a:t>
           </a:r>
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
               <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
               <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
             </a:rPr>
-            <a:t>仮想マシン状態初期化処理関数</a:t>
+            <a:t>仮想マシン状態調停初期化処理関数</a:t>
           </a:r>
           <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
             <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
@@ -4143,7 +4143,7 @@
               <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
               <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
             </a:rPr>
-            <a:t>vdg_pvehstsif_64msm()</a:t>
+            <a:t>vdg_pvehstsjdgif_64msm()</a:t>
           </a:r>
           <a:r>
             <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" baseline="0">
@@ -4157,7 +4157,7 @@
               <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
               <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
             </a:rPr>
-            <a:t>仮想マシン状態定期処理関数</a:t>
+            <a:t>仮想マシン状態調停定期処理関数</a:t>
           </a:r>
           <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
             <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
@@ -4170,14 +4170,14 @@
               <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
               <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
             </a:rPr>
-            <a:t>u1g_pvehstsif_stop      </a:t>
+            <a:t>u1g_pvehstsjdgif_stop      </a:t>
           </a:r>
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
               <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
               <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
             </a:rPr>
-            <a:t>仮想マシン停止状態</a:t>
+            <a:t>仮想マシン停止状態調停結果</a:t>
           </a:r>
           <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
             <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
@@ -4190,14 +4190,14 @@
               <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
               <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
             </a:rPr>
-            <a:t>u1g_pvehstsif_run       </a:t>
+            <a:t>u1g_pvehstsjdgif_run       </a:t>
           </a:r>
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
               <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
               <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
             </a:rPr>
-            <a:t>仮想マシン走行状態</a:t>
+            <a:t>仮想マシン走行状態調停結果</a:t>
           </a:r>
           <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
             <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
@@ -4210,14 +4210,14 @@
               <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
               <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
             </a:rPr>
-            <a:t>u1g_pvehstsif_spdup     </a:t>
+            <a:t>u1g_pvehstsjdgif_spdup     </a:t>
           </a:r>
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
               <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
               <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
             </a:rPr>
-            <a:t>仮想マシン加速状態</a:t>
+            <a:t>仮想マシン加速状態調停結果</a:t>
           </a:r>
           <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
             <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
@@ -4230,14 +4230,14 @@
               <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
               <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
             </a:rPr>
-            <a:t>u1g_pvehstsif_spddw     </a:t>
+            <a:t>u1g_pvehstsjdgif_spddw     </a:t>
           </a:r>
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
               <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
               <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
             </a:rPr>
-            <a:t>仮想マシン減速状態</a:t>
+            <a:t>仮想マシン減速状態調停結果</a:t>
           </a:r>
           <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
             <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
@@ -4250,14 +4250,14 @@
               <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
               <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
             </a:rPr>
-            <a:t>u1g_pvehstsif_enst      </a:t>
+            <a:t>u1g_pvehstsjdgif_enst      </a:t>
           </a:r>
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
               <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
               <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
             </a:rPr>
-            <a:t>仮想マシンエンジンストール状態</a:t>
+            <a:t>仮想マシンエンスト状態調停結果</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -4333,16 +4333,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>34</xdr:col>
-      <xdr:colOff>217715</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>56830</xdr:rowOff>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>4803</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>801</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>40</xdr:col>
-      <xdr:colOff>527477</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>154483</xdr:rowOff>
+      <xdr:col>41</xdr:col>
+      <xdr:colOff>314565</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>11206</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4351,8 +4351,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="27976286" y="2179544"/>
-          <a:ext cx="5208334" cy="1335903"/>
+          <a:off x="28243627" y="1681683"/>
+          <a:ext cx="5150703" cy="1018935"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4497,16 +4497,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>34</xdr:col>
-      <xdr:colOff>296636</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>141194</xdr:rowOff>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>5283</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>6724</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>40</xdr:col>
-      <xdr:colOff>606398</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>67397</xdr:rowOff>
+      <xdr:col>41</xdr:col>
+      <xdr:colOff>315045</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4515,8 +4515,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="27823886" y="3570194"/>
-          <a:ext cx="5167512" cy="1297803"/>
+          <a:off x="28244107" y="3032312"/>
+          <a:ext cx="5150703" cy="1337982"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4681,16 +4681,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>34</xdr:col>
-      <xdr:colOff>382361</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>93569</xdr:rowOff>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>12566</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>15128</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>40</xdr:col>
-      <xdr:colOff>692123</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>19772</xdr:rowOff>
+      <xdr:col>41</xdr:col>
+      <xdr:colOff>322328</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>11207</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4699,8 +4699,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="27909611" y="5065619"/>
-          <a:ext cx="5167512" cy="1297803"/>
+          <a:off x="28251390" y="4721599"/>
+          <a:ext cx="5150703" cy="1004608"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4845,16 +4845,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>34</xdr:col>
-      <xdr:colOff>382361</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>17369</xdr:rowOff>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>1361</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>163047</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>40</xdr:col>
-      <xdr:colOff>692123</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>115022</xdr:rowOff>
+      <xdr:col>41</xdr:col>
+      <xdr:colOff>311123</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4863,8 +4863,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="27909611" y="6532469"/>
-          <a:ext cx="5167512" cy="1297803"/>
+          <a:off x="28240185" y="6046135"/>
+          <a:ext cx="5150703" cy="1181660"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5041,16 +5041,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>34</xdr:col>
-      <xdr:colOff>429986</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>93569</xdr:rowOff>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>4162</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>3922</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>40</xdr:col>
-      <xdr:colOff>739748</xdr:colOff>
-      <xdr:row>55</xdr:row>
-      <xdr:rowOff>19772</xdr:rowOff>
+      <xdr:col>41</xdr:col>
+      <xdr:colOff>313924</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>11206</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -5059,8 +5059,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="27957236" y="8151719"/>
-          <a:ext cx="5167512" cy="1297803"/>
+          <a:off x="28242986" y="7567893"/>
+          <a:ext cx="5150703" cy="1015813"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5217,16 +5217,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>266535</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>152482</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>805962</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>8381</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>607519</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>157093</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>4047</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>71454</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -5238,12 +5238,12 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipV="1">
-          <a:off x="11562064" y="2673806"/>
-          <a:ext cx="1954631" cy="4611"/>
+          <a:off x="11419533" y="2307988"/>
+          <a:ext cx="2463800" cy="63073"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst>
-            <a:gd name="adj1" fmla="val 50000"/>
+            <a:gd name="adj1" fmla="val 86038"/>
           </a:avLst>
         </a:prstGeom>
         <a:ln>
@@ -5269,16 +5269,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>266535</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>159370</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>805962</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>71454</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>715576</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>92586</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>1202</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>1153</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -5290,12 +5290,12 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11601285" y="2748979"/>
-          <a:ext cx="2068291" cy="1832263"/>
+          <a:off x="11419533" y="2371061"/>
+          <a:ext cx="2460955" cy="1344842"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst>
-            <a:gd name="adj1" fmla="val 76077"/>
+            <a:gd name="adj1" fmla="val 84230"/>
           </a:avLst>
         </a:prstGeom>
         <a:ln>
@@ -5321,16 +5321,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>266535</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>157309</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>805962</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>71454</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>528276</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>103783</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>8064</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>173912</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -5342,12 +5342,12 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11652573" y="2685097"/>
-          <a:ext cx="1888318" cy="3485378"/>
+          <a:off x="11419533" y="2371061"/>
+          <a:ext cx="2467817" cy="2755851"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst>
-            <a:gd name="adj1" fmla="val 76889"/>
+            <a:gd name="adj1" fmla="val 77676"/>
           </a:avLst>
         </a:prstGeom>
         <a:ln>
@@ -5373,16 +5373,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>266535</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>157309</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>805962</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>71454</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>690818</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>80354</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>2087</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>91037</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -5394,12 +5394,12 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11652573" y="2685097"/>
-          <a:ext cx="2050860" cy="5147142"/>
+          <a:off x="11294668" y="2256601"/>
+          <a:ext cx="2423419" cy="3885612"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst>
-            <a:gd name="adj1" fmla="val 63197"/>
+            <a:gd name="adj1" fmla="val 71270"/>
           </a:avLst>
         </a:prstGeom>
         <a:ln>
@@ -5425,16 +5425,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>266535</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>157309</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>805962</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>71454</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>708302</xdr:colOff>
-      <xdr:row>55</xdr:row>
-      <xdr:rowOff>64001</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>1254</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>172212</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -5446,12 +5446,12 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11652573" y="2685097"/>
-          <a:ext cx="2068344" cy="6647462"/>
+          <a:off x="11419533" y="2371061"/>
+          <a:ext cx="2461007" cy="5407544"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst>
-            <a:gd name="adj1" fmla="val 55452"/>
+            <a:gd name="adj1" fmla="val 64339"/>
           </a:avLst>
         </a:prstGeom>
         <a:ln>
@@ -5477,16 +5477,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>299117</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>43023</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>805962</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>82812</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>712536</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>73995</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>1825</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>84922</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -5498,12 +5498,12 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm rot="10800000">
-          <a:off x="11594646" y="4917582"/>
-          <a:ext cx="2027066" cy="5914060"/>
+          <a:off x="11419533" y="3797562"/>
+          <a:ext cx="2461578" cy="5308896"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst>
-            <a:gd name="adj1" fmla="val 50000"/>
+            <a:gd name="adj1" fmla="val 40289"/>
           </a:avLst>
         </a:prstGeom>
         <a:ln>
@@ -5529,16 +5529,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>299117</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>43024</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>805962</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>82812</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>709442</xdr:colOff>
-      <xdr:row>73</xdr:row>
-      <xdr:rowOff>13433</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>8057</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>92110</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -5550,12 +5550,12 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm rot="10800000">
-          <a:off x="11594646" y="4917583"/>
-          <a:ext cx="2023972" cy="7366291"/>
+          <a:off x="11419533" y="3797562"/>
+          <a:ext cx="2467810" cy="6554334"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst>
-            <a:gd name="adj1" fmla="val 50000"/>
+            <a:gd name="adj1" fmla="val 45387"/>
           </a:avLst>
         </a:prstGeom>
         <a:ln>
@@ -5581,16 +5581,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>299117</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>43024</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>805963</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>82813</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>653942</xdr:colOff>
-      <xdr:row>81</xdr:row>
-      <xdr:rowOff>141277</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>183</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>84012</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -5602,60 +5602,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm rot="10800000">
-          <a:off x="11594646" y="4917583"/>
-          <a:ext cx="1968472" cy="8838841"/>
-        </a:xfrm>
-        <a:prstGeom prst="bentConnector3">
-          <a:avLst>
-            <a:gd name="adj1" fmla="val 55123"/>
-          </a:avLst>
-        </a:prstGeom>
-        <a:ln>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>194432</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>144075</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>25</xdr:col>
-      <xdr:colOff>683559</xdr:colOff>
-      <xdr:row>55</xdr:row>
-      <xdr:rowOff>64001</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="78" name="カギ線コネクタ 77"/>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="17" idx="3"/>
-          <a:endCxn id="24" idx="1"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="18751373" y="2497310"/>
-          <a:ext cx="2102774" cy="6811544"/>
+          <a:off x="11419534" y="3797563"/>
+          <a:ext cx="2459935" cy="7784485"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst>
@@ -5686,80 +5634,28 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>23</xdr:col>
-      <xdr:colOff>176948</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>144075</xdr:rowOff>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>5602</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>25</xdr:col>
-      <xdr:colOff>683559</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>80354</xdr:rowOff>
+      <xdr:colOff>801221</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>167811</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="81" name="カギ線コネクタ 80"/>
+        <xdr:cNvPr id="78" name="カギ線コネクタ 77"/>
         <xdr:cNvCxnSpPr>
-          <a:stCxn id="16" idx="3"/>
+          <a:stCxn id="17" idx="3"/>
           <a:endCxn id="24" idx="1"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipV="1">
-          <a:off x="18733889" y="2497310"/>
-          <a:ext cx="2120258" cy="5315103"/>
-        </a:xfrm>
-        <a:prstGeom prst="bentConnector3">
-          <a:avLst>
-            <a:gd name="adj1" fmla="val 43129"/>
-          </a:avLst>
-        </a:prstGeom>
-        <a:ln>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>201706</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>85589</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>26</xdr:col>
-      <xdr:colOff>66324</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>92587</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="85" name="カギ線コネクタ 84"/>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="14" idx="3"/>
-          <a:endCxn id="25" idx="1"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="18979563" y="4684803"/>
-          <a:ext cx="2313904" cy="6998"/>
+          <a:off x="18566466" y="2190749"/>
+          <a:ext cx="2405343" cy="5204856"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst>
@@ -5790,31 +5686,2241 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>23</xdr:col>
-      <xdr:colOff>166806</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>85589</xdr:rowOff>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>5602</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>801221</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>86636</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="81" name="カギ線コネクタ 80"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="16" idx="3"/>
+          <a:endCxn id="24" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="18556942" y="2190749"/>
+          <a:ext cx="2414867" cy="3947063"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 86659"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>9526</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>1153</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>26</xdr:col>
-      <xdr:colOff>66324</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>83477</xdr:rowOff>
+      <xdr:colOff>8253</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>90392</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="85" name="カギ線コネクタ 84"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="14" idx="3"/>
+          <a:endCxn id="25" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="18566467" y="3531006"/>
+          <a:ext cx="2419198" cy="257327"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 50000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>9526</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>90392</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>8253</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>1421</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
         <xdr:cNvPr id="89" name="カギ線コネクタ 88"/>
         <xdr:cNvCxnSpPr>
+          <a:stCxn id="15" idx="3"/>
           <a:endCxn id="25" idx="1"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipV="1">
-          <a:off x="18944663" y="4684803"/>
-          <a:ext cx="2348804" cy="1943710"/>
+          <a:off x="18566467" y="3788333"/>
+          <a:ext cx="2419198" cy="1087647"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst>
-            <a:gd name="adj1" fmla="val 92953"/>
+            <a:gd name="adj1" fmla="val 50000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>103909</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>-1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>554182</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>86590</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="51" name="カギ線コネクタ 50"/>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="16200000" flipH="1">
+          <a:off x="5377296" y="5619749"/>
+          <a:ext cx="1298863" cy="450273"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 295333"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>8381</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>8253</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>90392</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="80" name="カギ線コネクタ 79"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="13" idx="3"/>
+          <a:endCxn id="25" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="18556941" y="2193528"/>
+          <a:ext cx="2428724" cy="1594805"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 50000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>90392</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>8253</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>167811</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="84" name="カギ線コネクタ 83"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="17" idx="3"/>
+          <a:endCxn id="25" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="18566466" y="3788333"/>
+          <a:ext cx="2419199" cy="3607272"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 90762"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>159998</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>803740</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>84921</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="97" name="カギ線コネクタ 96"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="27" idx="1"/>
+          <a:endCxn id="18" idx="3"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="10800000" flipV="1">
+          <a:off x="18556942" y="7219704"/>
+          <a:ext cx="2417386" cy="1437717"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 50000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>159999</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>803740</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>87707</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="101" name="カギ線コネクタ 100"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="27" idx="1"/>
+          <a:endCxn id="20" idx="3"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="10800000" flipV="1">
+          <a:off x="18566466" y="7219705"/>
+          <a:ext cx="2407862" cy="2617120"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 50000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>159999</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>803741</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>84012</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="107" name="カギ線コネクタ 106"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="27" idx="1"/>
+          <a:endCxn id="19" idx="3"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="10800000" flipV="1">
+          <a:off x="18556942" y="7219705"/>
+          <a:ext cx="2417387" cy="3790042"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 50000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>9526</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>1421</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>803740</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>159999</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="120" name="カギ線コネクタ 119"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="15" idx="3"/>
+          <a:endCxn id="27" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="18566467" y="4875980"/>
+          <a:ext cx="2407861" cy="2343725"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 68150"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>9526</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>1153</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>803740</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>159999</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="123" name="カギ線コネクタ 122"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="14" idx="3"/>
+          <a:endCxn id="27" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="18566467" y="3531006"/>
+          <a:ext cx="2407861" cy="3688699"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 72804"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>8381</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>803740</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>159999</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="126" name="カギ線コネクタ 125"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="13" idx="3"/>
+          <a:endCxn id="27" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="18556941" y="2193528"/>
+          <a:ext cx="2417387" cy="5026177"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 81058"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>2183</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>166911</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="147" name="テキスト ボックス 146"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13765808" y="11996961"/>
+          <a:ext cx="4855567" cy="2747739"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent4">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>acfmdispif.h</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>vdg_acfmdispif_pwon()     </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>確定演算値公開初期化処理</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>vdg_acfmdispif_16msm()    </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>確定演算値公開定期処理関数</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>s1g_acfmdispif_</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>aclthlpct</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>  </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>確定演算アクセル公開値 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>1-100[%]</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>s1g_acfmdispif_</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>brkpdlpct</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>  </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>確定演算ブレーキ公開値   </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>1-100[%]</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>s1g_acfmdispif_</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>clthpdlpct</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>確定クラッチ公開値 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>1-100[%]</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>s1g_acfmdispif_eng        </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>エンジン許可調停結果公開値</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>　</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>OFF,ON[-]</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>s1g_acfmdispif_sht</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>        シフト遷移調停結果公開値   </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>OFF,ON[-]</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>s1g_acfmdispif_</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>ovrvsts    </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>オーバーレブ調停結果公開値　</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>OFF,ON[-]</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>s1g_acfmdispif_</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>clthszsts  </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>クラッチ焼き付き調停結果公開値</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>OFF,ON[-]</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>s1g_acfmdispif_</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>brkszsts   </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>ブレーキ焼き付き調停結果公開値 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>OFF,ON[-]</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>s1g_acfmdispif_</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>enststs    </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>エンジンストール調停結果公開値 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>OFF,ON[-]</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>s1g_acfmdispif_</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>ovrhet     </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>オーバーヒート状態警告公開値 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>OFF,ON[-]</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>s1g_acfmdispif_</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>snserr     </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>センサー状態警告公開値 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>OFF,ON[-]</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>5601</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>801221</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>167499</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="148" name="カギ線コネクタ 147"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="24" idx="1"/>
+          <a:endCxn id="147" idx="3"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="10800000" flipV="1">
+          <a:off x="18556941" y="2190748"/>
+          <a:ext cx="2414868" cy="10919545"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 91299"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>90391</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>8253</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>167499</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="155" name="カギ線コネクタ 154"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="25" idx="1"/>
+          <a:endCxn id="147" idx="3"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="10800000" flipV="1">
+          <a:off x="18556941" y="3788332"/>
+          <a:ext cx="2428724" cy="9321961"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 50000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>102</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>13325</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>167500</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="159" name="カギ線コネクタ 158"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="26" idx="1"/>
+          <a:endCxn id="147" idx="3"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="10800000" flipV="1">
+          <a:off x="18556942" y="5378926"/>
+          <a:ext cx="2433795" cy="7731368"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 50000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>159998</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>803741</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>167499</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="162" name="カギ線コネクタ 161"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="27" idx="1"/>
+          <a:endCxn id="147" idx="3"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="10800000" flipV="1">
+          <a:off x="18556942" y="7219704"/>
+          <a:ext cx="2417387" cy="5890589"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 7353"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>2361</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>165603</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>97</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="174" name="テキスト ボックス 173"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13765986" y="15081753"/>
+          <a:ext cx="4864914" cy="1548897"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent4">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>avehstsif.h</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>vdg_avehstsif_pwon()   </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>仮想マシン状態初期化処理</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>vdg_avehstsif_64msm()  </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>仮想マシン状態定期処理</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>vdg_avehstsif_stop     </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>仮想マシン停止状態</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>vdg_avehstsif_run      </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>仮想マシン走行状態</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>vdg_avehstsif_spdup     </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>仮想マシン加速状態</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>vdg_avehstsif_spddw     </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>仮想マシン減速状態</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>vdg_avehstsif_enst     </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>仮想マシンエンスト状態</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>164976</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>13728</xdr:colOff>
+      <xdr:row>92</xdr:row>
+      <xdr:rowOff>82801</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="175" name="カギ線コネクタ 174"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="29" idx="1"/>
+          <a:endCxn id="174" idx="3"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="10800000" flipV="1">
+          <a:off x="18566466" y="9409829"/>
+          <a:ext cx="2424674" cy="6137090"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 50000"/>
           </a:avLst>
         </a:prstGeom>
         <a:ln>
@@ -6092,7 +8198,31 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </a:spPr>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">

--- a/暫定案.xlsx
+++ b/暫定案.xlsx
@@ -12,7 +12,8 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="15360" windowHeight="7770"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="1.入出力" sheetId="2" r:id="rId1"/>
+    <sheet name="4.詳細" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>BSW</t>
     <phoneticPr fontId="1"/>
@@ -44,6 +45,315 @@
   </si>
   <si>
     <t>あ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アクセル開度</t>
+    <rPh sb="4" eb="5">
+      <t>ヒラ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ブレーキ開度</t>
+    <rPh sb="4" eb="5">
+      <t>ヒラ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>クラッチ開度</t>
+    <rPh sb="4" eb="5">
+      <t>ヒラ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ギアポジション</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>イグニッションスイッチ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>iphoneカウンター</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>１．入出力考える</t>
+    <rPh sb="2" eb="5">
+      <t>ニュウシュツリョク</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>カンガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>２．機能考える</t>
+    <rPh sb="2" eb="4">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>カンガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>３．層分け考える</t>
+    <rPh sb="2" eb="3">
+      <t>ソウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>カンガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>４．詳細考える</t>
+    <rPh sb="2" eb="4">
+      <t>ショウサイ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>カンガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>仮想マシン速度</t>
+    <rPh sb="0" eb="2">
+      <t>カソウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ソクド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>仮想マシンエンジン回転数</t>
+    <rPh sb="0" eb="2">
+      <t>カソウ</t>
+    </rPh>
+    <rPh sb="9" eb="12">
+      <t>カイテンスウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>仮想マシンギア状態</t>
+    <rPh sb="0" eb="2">
+      <t>カソウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ジョウタイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アクセル表示</t>
+    <rPh sb="4" eb="6">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ブレーキ表示</t>
+    <rPh sb="4" eb="6">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>クラッチ表示</t>
+    <rPh sb="4" eb="6">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>仮想マシン駆動許可表示</t>
+    <rPh sb="0" eb="2">
+      <t>カソウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>クドウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>キョカ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>シフト遷移許可表示</t>
+    <rPh sb="3" eb="5">
+      <t>センイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>キョカ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>オーバーレブ状態表示</t>
+    <rPh sb="6" eb="8">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>クラッチ焼き付き状態表示</t>
+    <rPh sb="4" eb="5">
+      <t>ヤ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ブレーキ焼き付き状態表示</t>
+    <rPh sb="4" eb="5">
+      <t>ヤ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>エンジンストール状態表示</t>
+    <rPh sb="8" eb="10">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>オーバーヒート状態表示</t>
+    <rPh sb="7" eb="9">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>センサー状態表示</t>
+    <rPh sb="4" eb="6">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>仮想マシン停止状態</t>
+    <rPh sb="0" eb="2">
+      <t>カソウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>テイシ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ジョウタイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>仮想マシン走行状態</t>
+    <rPh sb="0" eb="2">
+      <t>カソウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ソウコウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ジョウタイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>仮想マシン加速状態</t>
+    <rPh sb="0" eb="2">
+      <t>カソウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>カソク</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ジョウタイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>仮想マシン減速状態</t>
+    <rPh sb="0" eb="2">
+      <t>カソウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ゲンソク</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ジョウタイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>仮想マシンエンスト状態</t>
+    <rPh sb="0" eb="2">
+      <t>カソウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ジョウタイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>仮想マシンイグニッションステータス状態</t>
+    <rPh sb="0" eb="2">
+      <t>カソウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ジョウタイ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -82,12 +392,24 @@
       <charset val="128"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -104,7 +426,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -113,6 +435,15 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -141,6 +472,245 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>676276</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>9526</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>676276</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="正方形/長方形 1"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4791076" y="866776"/>
+          <a:ext cx="1371600" cy="7362824"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" vert="wordArtVertRtl" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="5400"/>
+            <a:t>ZUN</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="5400"/>
+            <a:t>車</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>231321</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>149679</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>571499</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>54429</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="正方形/長方形 4"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2272392" y="680358"/>
+          <a:ext cx="1700893" cy="258535"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>仮想システム全体入出力</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>108856</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>340179</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>13605</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="正方形/長方形 5"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3401786" y="2585356"/>
+          <a:ext cx="1700893" cy="258535"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>INPUT</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>16328</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>111578</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>356507</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>16327</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="正方形/長方形 6"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7500257" y="819149"/>
+          <a:ext cx="1700893" cy="258535"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>OUTPUT</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>19050</xdr:colOff>
       <xdr:row>2</xdr:row>
@@ -149,8 +719,8 @@
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>762001</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>9526</xdr:rowOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -159,8 +729,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6496050" y="342900"/>
-          <a:ext cx="4791076" cy="352426"/>
+          <a:off x="6550479" y="353786"/>
+          <a:ext cx="4825093" cy="272143"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -217,14 +787,14 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>517</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>167753</xdr:rowOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>167751</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>805962</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>152047</xdr:rowOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>152045</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -233,7 +803,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6531946" y="1759789"/>
+          <a:off x="6531946" y="3351822"/>
           <a:ext cx="4887587" cy="1222544"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -567,15 +1137,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>9003</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>173814</xdr:rowOff>
+      <xdr:colOff>10416</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>9230</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>805962</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>168702</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>552</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>167365</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -584,8 +1154,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6540432" y="3357885"/>
-          <a:ext cx="4879101" cy="879353"/>
+          <a:off x="6541845" y="4962230"/>
+          <a:ext cx="4888707" cy="4403564"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -646,7 +1216,43 @@
               <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>u2g_bbsw2iosif_vel        </a:t>
+            <a:t>u2g_bbsw2iosif_vel       </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>swift</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>用</a:t>
           </a:r>
           <a:r>
             <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
@@ -658,7 +1264,7 @@
               <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>仮想マシン速度 </a:t>
+            <a:t>マシン速度 </a:t>
           </a:r>
           <a:r>
             <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
@@ -689,11 +1295,35 @@
             <a:t>        </a:t>
           </a:r>
           <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>swift</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>用</a:t>
+          </a:r>
+          <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" baseline="0">
               <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
               <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
             </a:rPr>
-            <a:t>仮想マシン回転数 </a:t>
+            <a:t>マシン回転数 </a:t>
           </a:r>
           <a:r>
             <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" baseline="0">
@@ -719,11 +1349,35 @@
             <a:t>       </a:t>
           </a:r>
           <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>swift</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>用</a:t>
+          </a:r>
+          <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" baseline="0">
               <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
               <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
             </a:rPr>
-            <a:t>仮想マシンギア状態 </a:t>
+            <a:t>マシンギア状態 </a:t>
           </a:r>
           <a:r>
             <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" baseline="0">
@@ -734,13 +1388,1428 @@
           </a:r>
         </a:p>
         <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>u2g_bbsw2iosif_aclthlpct  </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>swift</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>用</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>アクセル開度</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>1-100[%]</a:t>
+          </a:r>
           <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" baseline="0">
             <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
             <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
           </a:endParaRPr>
         </a:p>
         <a:p>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>u2g_bbsw2iosif_brkpdlpct  </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>swift</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>用</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>ブレーキ開度</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>1-100[%]</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>u2g_bbsw2iosif_clthpdlpct </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>swift</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>用</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>クラッチ開度</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>1-100[%]</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>u2g_bbsw2iosif_</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>eng        </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>swift</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>用</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>エンジン許可状態</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>OFF,ON[-]</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>u2g_bbsw2iosif_</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>sht        </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>swift</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>用</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>シフト遷移許可状態</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>OFF,ON[-]</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>u2g_bbsw2iosif_ovrvsts    </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>swift</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>用</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>オーバーレブ調停結果</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>OFF,ON[-]</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>u2g_bbsw2iosif_clthszsts  </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>swift</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>用</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>クラッチ焼き付き調停結果</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>OFF,ON[-]</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>u2g_bbsw2iosif_brkszsts   </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>swift</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>用</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>ブレーキ焼き付き調停結果</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>OFF,ON[-]</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>u2g_bbsw2iosif_enststs    </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>swift</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>用</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>エンジンストール調停結果</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>OFF,ON[-]</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>u2g_bbsw2iosif_ovrhet     </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>swift</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>用</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>オーバーヒート状態警告値</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>OFF,ON[-]</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>u2g_bbsw2iosif_snserr     </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>swift</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>用</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>センサー状態警告値</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>OFF,ON[-]</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>u2g_bbsw2iosif_</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>stopsts    </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>swift</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>用</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>マシン停止状態</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>OFF,ON[-]</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>u2g_bbsw2iosif_</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>runsts     </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>swift</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>用</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>マシン走行状態</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>OFF,ON[-]</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>u2g_bbsw2iosif_</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>spdupsts   </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>swift</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>用</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>マシン加速状態</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>OFF,ON[-]</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>u2g_bbsw2iosif_</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>spddwsts   </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>swift</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>用</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>マシン減速状態</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>OFF,ON[-]</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>u2g_bbsw2iosif_</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>enststs    </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>swift</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>用</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>マシンエンスト状態</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>OFF,ON[-]</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
+            <a:effectLst/>
             <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
             <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
           </a:endParaRPr>
@@ -752,15 +2821,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4550</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>168272</xdr:rowOff>
+      <xdr:colOff>15756</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>9707</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>7328</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>152047</xdr:rowOff>
+      <xdr:colOff>18534</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>161569</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -769,8 +2838,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6535979" y="4590593"/>
-          <a:ext cx="4901349" cy="868240"/>
+          <a:off x="6547185" y="9738814"/>
+          <a:ext cx="4901349" cy="859434"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -949,15 +3018,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>809734</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>164488</xdr:rowOff>
+      <xdr:colOff>803332</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>16169</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>805963</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>152046</xdr:rowOff>
+      <xdr:colOff>799561</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>175175</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -966,8 +3035,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6524734" y="5825059"/>
-          <a:ext cx="4894800" cy="1048916"/>
+          <a:off x="6518332" y="1961990"/>
+          <a:ext cx="4894800" cy="1043471"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1272,16 +3341,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>809575</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>164195</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>13958</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>2270</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>7328</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>167409</xdr:rowOff>
+      <xdr:colOff>18534</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>5484</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1290,8 +3359,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6524575" y="7063016"/>
-          <a:ext cx="4912753" cy="533893"/>
+          <a:off x="6545387" y="10969627"/>
+          <a:ext cx="4903147" cy="533893"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1382,89 +3451,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>182334</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>161926</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>800100</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>142876</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="12" name="テキスト ボックス 11"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="13136334" y="333376"/>
-          <a:ext cx="6285141" cy="323850"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="accent4">
-            <a:lumMod val="60000"/>
-            <a:lumOff val="40000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:solidFill>
-            <a:schemeClr val="lt1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
-              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
-              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
-            </a:rPr>
-            <a:t>SAC</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
-            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
-            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>17</xdr:col>
       <xdr:colOff>4047</xdr:colOff>
-      <xdr:row>10</xdr:row>
+      <xdr:row>23</xdr:row>
       <xdr:rowOff>8479</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>23</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>8282</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1668,13 +3663,13 @@
     <xdr:from>
       <xdr:col>17</xdr:col>
       <xdr:colOff>1202</xdr:colOff>
-      <xdr:row>18</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>2305</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>23</xdr:col>
       <xdr:colOff>9526</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>37</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1875,13 +3870,13 @@
     <xdr:from>
       <xdr:col>17</xdr:col>
       <xdr:colOff>8064</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>39</xdr:row>
       <xdr:rowOff>9738</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>23</xdr:col>
       <xdr:colOff>9526</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>161192</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2096,13 +4091,13 @@
     <xdr:from>
       <xdr:col>17</xdr:col>
       <xdr:colOff>2087</xdr:colOff>
-      <xdr:row>34</xdr:row>
+      <xdr:row>47</xdr:row>
       <xdr:rowOff>5182</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>23</xdr:col>
       <xdr:colOff>1</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>52</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2288,13 +4283,13 @@
     <xdr:from>
       <xdr:col>17</xdr:col>
       <xdr:colOff>1254</xdr:colOff>
-      <xdr:row>41</xdr:row>
+      <xdr:row>54</xdr:row>
       <xdr:rowOff>6340</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>23</xdr:col>
       <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>59</xdr:row>
       <xdr:rowOff>161192</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2500,13 +4495,13 @@
     <xdr:from>
       <xdr:col>17</xdr:col>
       <xdr:colOff>1825</xdr:colOff>
-      <xdr:row>49</xdr:row>
+      <xdr:row>62</xdr:row>
       <xdr:rowOff>1326</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>23</xdr:col>
       <xdr:colOff>1</xdr:colOff>
-      <xdr:row>53</xdr:row>
+      <xdr:row>66</xdr:row>
       <xdr:rowOff>168518</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2686,13 +4681,13 @@
     <xdr:from>
       <xdr:col>17</xdr:col>
       <xdr:colOff>182</xdr:colOff>
-      <xdr:row>62</xdr:row>
+      <xdr:row>75</xdr:row>
       <xdr:rowOff>168021</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>23</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>68</xdr:row>
+      <xdr:row>81</xdr:row>
       <xdr:rowOff>1</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2869,13 +4864,13 @@
     <xdr:from>
       <xdr:col>17</xdr:col>
       <xdr:colOff>8057</xdr:colOff>
-      <xdr:row>56</xdr:row>
+      <xdr:row>69</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>23</xdr:col>
       <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>61</xdr:row>
+      <xdr:row>74</xdr:row>
       <xdr:rowOff>7327</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -3058,8 +5053,8 @@
     <xdr:to>
       <xdr:col>32</xdr:col>
       <xdr:colOff>657393</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3069,7 +5064,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="20533099" y="253813"/>
-          <a:ext cx="6032294" cy="441512"/>
+          <a:ext cx="6032294" cy="384362"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3197,13 +5192,13 @@
     <xdr:from>
       <xdr:col>25</xdr:col>
       <xdr:colOff>801221</xdr:colOff>
-      <xdr:row>10</xdr:row>
+      <xdr:row>23</xdr:row>
       <xdr:rowOff>11203</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>31</xdr:col>
       <xdr:colOff>795618</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -3357,13 +5352,13 @@
     <xdr:from>
       <xdr:col>26</xdr:col>
       <xdr:colOff>8253</xdr:colOff>
-      <xdr:row>18</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>12695</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>32</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>40</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -3570,13 +5565,13 @@
     <xdr:from>
       <xdr:col>26</xdr:col>
       <xdr:colOff>13324</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>42</xdr:row>
       <xdr:rowOff>205</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>32</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>35</xdr:row>
+      <xdr:row>48</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -3733,14 +5728,14 @@
     <xdr:from>
       <xdr:col>25</xdr:col>
       <xdr:colOff>803740</xdr:colOff>
-      <xdr:row>36</xdr:row>
+      <xdr:row>49</xdr:row>
       <xdr:rowOff>163115</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>32</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>156884</xdr:rowOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3749,8 +5744,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="20974328" y="6214291"/>
-          <a:ext cx="4844025" cy="2010828"/>
+          <a:off x="21044365" y="8564165"/>
+          <a:ext cx="4863635" cy="2237185"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3975,7 +5970,28 @@
           </a:endParaRPr>
         </a:p>
         <a:p>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>u1g_psimbrdig_igswsts</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" baseline="0">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>      </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" baseline="0">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>仮想演算用イグニッションスイッチ状態</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
             <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
             <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
           </a:endParaRPr>
@@ -3988,13 +6004,13 @@
     <xdr:from>
       <xdr:col>25</xdr:col>
       <xdr:colOff>773932</xdr:colOff>
-      <xdr:row>75</xdr:row>
+      <xdr:row>88</xdr:row>
       <xdr:rowOff>171089</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>32</xdr:col>
       <xdr:colOff>267266</xdr:colOff>
-      <xdr:row>82</xdr:row>
+      <xdr:row>95</xdr:row>
       <xdr:rowOff>9847</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -4055,13 +6071,13 @@
     <xdr:from>
       <xdr:col>26</xdr:col>
       <xdr:colOff>13728</xdr:colOff>
-      <xdr:row>51</xdr:row>
+      <xdr:row>65</xdr:row>
       <xdr:rowOff>4982</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>32</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>60</xdr:row>
+      <xdr:row>74</xdr:row>
       <xdr:rowOff>156882</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -4071,8 +6087,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="20991140" y="8577482"/>
-          <a:ext cx="4827213" cy="1664694"/>
+          <a:off x="21063978" y="11149232"/>
+          <a:ext cx="4844022" cy="1694950"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4118,12 +6134,29 @@
           </a:r>
         </a:p>
         <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
-              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
-              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
-            </a:rPr>
-            <a:t>vdg_pvehstsjdgif_pwon()    </a:t>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>vdg_pvehstsjdgif_pwon()  </a:t>
           </a:r>
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
@@ -4132,12 +6165,41 @@
             </a:rPr>
             <a:t>仮想マシン状態調停初期化処理関数</a:t>
           </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>OFF,ON[-]</a:t>
+          </a:r>
           <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
             <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
             <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
           </a:endParaRPr>
         </a:p>
         <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
           <a:r>
             <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
               <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
@@ -4150,7 +6212,7 @@
               <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
               <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
             </a:rPr>
-            <a:t>   </a:t>
+            <a:t> </a:t>
           </a:r>
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" baseline="0">
@@ -4159,18 +6221,47 @@
             </a:rPr>
             <a:t>仮想マシン状態調停定期処理関数</a:t>
           </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>OFF,ON[-]</a:t>
+          </a:r>
           <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
             <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
             <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
           </a:endParaRPr>
         </a:p>
         <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
-              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
-              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
-            </a:rPr>
-            <a:t>u1g_pvehstsjdgif_stop      </a:t>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>u1g_pvehstsjdgif_stop    </a:t>
           </a:r>
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
@@ -4179,18 +6270,47 @@
             </a:rPr>
             <a:t>仮想マシン停止状態調停結果</a:t>
           </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>OFF,ON[-]</a:t>
+          </a:r>
           <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
             <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
             <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
           </a:endParaRPr>
         </a:p>
         <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
-              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
-              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
-            </a:rPr>
-            <a:t>u1g_pvehstsjdgif_run       </a:t>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>u1g_pvehstsjdgif_run     </a:t>
           </a:r>
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
@@ -4199,18 +6319,47 @@
             </a:rPr>
             <a:t>仮想マシン走行状態調停結果</a:t>
           </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>OFF,ON[-]</a:t>
+          </a:r>
           <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
             <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
             <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
           </a:endParaRPr>
         </a:p>
         <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
-              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
-              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
-            </a:rPr>
-            <a:t>u1g_pvehstsjdgif_spdup     </a:t>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>u1g_pvehstsjdgif_spdup   </a:t>
           </a:r>
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
@@ -4219,18 +6368,47 @@
             </a:rPr>
             <a:t>仮想マシン加速状態調停結果</a:t>
           </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>OFF,ON[-]</a:t>
+          </a:r>
           <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
             <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
             <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
           </a:endParaRPr>
         </a:p>
         <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
-              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
-              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
-            </a:rPr>
-            <a:t>u1g_pvehstsjdgif_spddw     </a:t>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>u1g_pvehstsjdgif_spddw   </a:t>
           </a:r>
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
@@ -4239,18 +6417,47 @@
             </a:rPr>
             <a:t>仮想マシン減速状態調停結果</a:t>
           </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>OFF,ON[-]</a:t>
+          </a:r>
           <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
             <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
             <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
           </a:endParaRPr>
         </a:p>
         <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
-              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
-              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
-            </a:rPr>
-            <a:t>u1g_pvehstsjdgif_enst      </a:t>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>u1g_pvehstsjdgif_enst    </a:t>
           </a:r>
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
@@ -4259,6 +6466,21 @@
             </a:rPr>
             <a:t>仮想マシンエンスト状態調停結果</a:t>
           </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>OFF,ON[-]</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
+            <a:effectLst/>
+          </a:endParaRPr>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -4268,13 +6490,13 @@
     <xdr:from>
       <xdr:col>25</xdr:col>
       <xdr:colOff>765214</xdr:colOff>
-      <xdr:row>69</xdr:row>
+      <xdr:row>82</xdr:row>
       <xdr:rowOff>72664</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>32</xdr:col>
       <xdr:colOff>258548</xdr:colOff>
-      <xdr:row>75</xdr:row>
+      <xdr:row>88</xdr:row>
       <xdr:rowOff>88313</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -4335,13 +6557,13 @@
     <xdr:from>
       <xdr:col>35</xdr:col>
       <xdr:colOff>4803</xdr:colOff>
-      <xdr:row>10</xdr:row>
+      <xdr:row>23</xdr:row>
       <xdr:rowOff>801</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>41</xdr:col>
       <xdr:colOff>314565</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>11206</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -4499,13 +6721,13 @@
     <xdr:from>
       <xdr:col>35</xdr:col>
       <xdr:colOff>5283</xdr:colOff>
-      <xdr:row>18</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>6724</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>41</xdr:col>
       <xdr:colOff>315045</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>39</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -4683,13 +6905,13 @@
     <xdr:from>
       <xdr:col>35</xdr:col>
       <xdr:colOff>12566</xdr:colOff>
-      <xdr:row>28</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>15128</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>41</xdr:col>
       <xdr:colOff>322328</xdr:colOff>
-      <xdr:row>34</xdr:row>
+      <xdr:row>47</xdr:row>
       <xdr:rowOff>11207</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -4847,13 +7069,13 @@
     <xdr:from>
       <xdr:col>35</xdr:col>
       <xdr:colOff>1361</xdr:colOff>
-      <xdr:row>35</xdr:row>
+      <xdr:row>48</xdr:row>
       <xdr:rowOff>163047</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>41</xdr:col>
       <xdr:colOff>311123</xdr:colOff>
-      <xdr:row>43</xdr:row>
+      <xdr:row>56</xdr:row>
       <xdr:rowOff>1</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -5043,13 +7265,13 @@
     <xdr:from>
       <xdr:col>35</xdr:col>
       <xdr:colOff>4162</xdr:colOff>
-      <xdr:row>45</xdr:row>
+      <xdr:row>58</xdr:row>
       <xdr:rowOff>3922</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>41</xdr:col>
       <xdr:colOff>313924</xdr:colOff>
-      <xdr:row>51</xdr:row>
+      <xdr:row>64</xdr:row>
       <xdr:rowOff>11206</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -5219,14 +7441,14 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>805962</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>8381</xdr:rowOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>71451</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
       <xdr:colOff>4047</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>71454</xdr:rowOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>8381</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -5237,13 +7459,13 @@
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="11419533" y="2307988"/>
-          <a:ext cx="2463800" cy="63073"/>
+        <a:xfrm>
+          <a:off x="11419533" y="3963094"/>
+          <a:ext cx="2463800" cy="644501"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst>
-            <a:gd name="adj1" fmla="val 86038"/>
+            <a:gd name="adj1" fmla="val 53127"/>
           </a:avLst>
         </a:prstGeom>
         <a:ln>
@@ -5271,13 +7493,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>805962</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>71454</xdr:rowOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>71451</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
       <xdr:colOff>1202</xdr:colOff>
-      <xdr:row>21</xdr:row>
+      <xdr:row>34</xdr:row>
       <xdr:rowOff>1153</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -5290,12 +7512,12 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11419533" y="2371061"/>
-          <a:ext cx="2460955" cy="1344842"/>
+          <a:off x="11419533" y="3963094"/>
+          <a:ext cx="2460955" cy="2052416"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst>
-            <a:gd name="adj1" fmla="val 84230"/>
+            <a:gd name="adj1" fmla="val 64481"/>
           </a:avLst>
         </a:prstGeom>
         <a:ln>
@@ -5323,13 +7545,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>805962</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>71454</xdr:rowOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>71451</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
       <xdr:colOff>8064</xdr:colOff>
-      <xdr:row>28</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>173912</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -5342,12 +7564,12 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11419533" y="2371061"/>
-          <a:ext cx="2467817" cy="2755851"/>
+          <a:off x="11419533" y="3963094"/>
+          <a:ext cx="2467817" cy="3463425"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst>
-            <a:gd name="adj1" fmla="val 77676"/>
+            <a:gd name="adj1" fmla="val 78100"/>
           </a:avLst>
         </a:prstGeom>
         <a:ln>
@@ -5375,14 +7597,14 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>805962</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>71454</xdr:rowOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>71451</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
       <xdr:colOff>2087</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>91037</xdr:rowOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>91038</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -5394,12 +7616,12 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11294668" y="2256601"/>
-          <a:ext cx="2423419" cy="3885612"/>
+          <a:off x="11419533" y="3963094"/>
+          <a:ext cx="2461840" cy="4795694"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst>
-            <a:gd name="adj1" fmla="val 71270"/>
+            <a:gd name="adj1" fmla="val 82081"/>
           </a:avLst>
         </a:prstGeom>
         <a:ln>
@@ -5427,14 +7649,14 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>805962</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>71454</xdr:rowOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>74173</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
       <xdr:colOff>1254</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>172212</xdr:rowOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>169491</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -5446,12 +7668,12 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11419533" y="2371061"/>
-          <a:ext cx="2461007" cy="5407544"/>
+          <a:off x="11331087" y="3846073"/>
+          <a:ext cx="2433792" cy="5924618"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst>
-            <a:gd name="adj1" fmla="val 64339"/>
+            <a:gd name="adj1" fmla="val 91876"/>
           </a:avLst>
         </a:prstGeom>
         <a:ln>
@@ -5477,16 +7699,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>805962</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>82812</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>553</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>88299</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>1825</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>84922</xdr:rowOff>
+      <xdr:colOff>1826</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>84923</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -5498,112 +7720,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm rot="10800000">
-          <a:off x="11419533" y="3797562"/>
-          <a:ext cx="2461578" cy="5308896"/>
-        </a:xfrm>
-        <a:prstGeom prst="bentConnector3">
-          <a:avLst>
-            <a:gd name="adj1" fmla="val 40289"/>
-          </a:avLst>
-        </a:prstGeom>
-        <a:ln>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>805962</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>82812</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>8057</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>92110</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="59" name="カギ線コネクタ 58"/>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="20" idx="1"/>
-          <a:endCxn id="7" idx="3"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="10800000">
-          <a:off x="11419533" y="3797562"/>
-          <a:ext cx="2467810" cy="6554334"/>
-        </a:xfrm>
-        <a:prstGeom prst="bentConnector3">
-          <a:avLst>
-            <a:gd name="adj1" fmla="val 45387"/>
-          </a:avLst>
-        </a:prstGeom>
-        <a:ln>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>805963</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>82813</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>183</xdr:colOff>
-      <xdr:row>65</xdr:row>
-      <xdr:rowOff>84012</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="62" name="カギ線コネクタ 61"/>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="19" idx="1"/>
-          <a:endCxn id="7" idx="3"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="10800000">
-          <a:off x="11419534" y="3797563"/>
-          <a:ext cx="2459935" cy="7784485"/>
+          <a:off x="11430553" y="7164013"/>
+          <a:ext cx="2450559" cy="4242053"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst>
@@ -5633,15 +7751,119 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>553</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>88299</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>8058</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>92111</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="59" name="カギ線コネクタ 58"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="20" idx="1"/>
+          <a:endCxn id="7" idx="3"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="10800000">
+          <a:off x="11430553" y="7164013"/>
+          <a:ext cx="2456791" cy="5487491"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 55473"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>552</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>88298</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>182</xdr:colOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>84011</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="62" name="カギ線コネクタ 61"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="19" idx="1"/>
+          <a:endCxn id="7" idx="3"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="10800000">
+          <a:off x="11430552" y="7164012"/>
+          <a:ext cx="2448916" cy="6717642"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 60590"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>23</xdr:col>
       <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>5602</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>25</xdr:col>
       <xdr:colOff>801221</xdr:colOff>
-      <xdr:row>43</xdr:row>
+      <xdr:row>56</xdr:row>
       <xdr:rowOff>167811</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -5687,13 +7909,13 @@
     <xdr:from>
       <xdr:col>23</xdr:col>
       <xdr:colOff>1</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>5602</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>25</xdr:col>
       <xdr:colOff>801221</xdr:colOff>
-      <xdr:row>36</xdr:row>
+      <xdr:row>49</xdr:row>
       <xdr:rowOff>86636</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -5739,13 +7961,13 @@
     <xdr:from>
       <xdr:col>23</xdr:col>
       <xdr:colOff>9526</xdr:colOff>
-      <xdr:row>21</xdr:row>
+      <xdr:row>34</xdr:row>
       <xdr:rowOff>1153</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>26</xdr:col>
       <xdr:colOff>8253</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>35</xdr:row>
       <xdr:rowOff>90392</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -5791,13 +8013,13 @@
     <xdr:from>
       <xdr:col>23</xdr:col>
       <xdr:colOff>9526</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>35</xdr:row>
       <xdr:rowOff>90392</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>26</xdr:col>
       <xdr:colOff>8253</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>42</xdr:row>
       <xdr:rowOff>1421</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -5843,13 +8065,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>103909</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>43</xdr:row>
       <xdr:rowOff>-1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>554182</xdr:colOff>
-      <xdr:row>37</xdr:row>
+      <xdr:row>50</xdr:row>
       <xdr:rowOff>86590</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -5892,13 +8114,13 @@
     <xdr:from>
       <xdr:col>23</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>8381</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>26</xdr:col>
       <xdr:colOff>8253</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>35</xdr:row>
       <xdr:rowOff>90392</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -5944,13 +8166,13 @@
     <xdr:from>
       <xdr:col>23</xdr:col>
       <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>35</xdr:row>
       <xdr:rowOff>90392</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>26</xdr:col>
       <xdr:colOff>8253</xdr:colOff>
-      <xdr:row>43</xdr:row>
+      <xdr:row>56</xdr:row>
       <xdr:rowOff>167811</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -5995,15 +8217,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>23</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>159998</xdr:rowOff>
+      <xdr:colOff>2</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>81558</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>25</xdr:col>
-      <xdr:colOff>803740</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>84921</xdr:rowOff>
+      <xdr:colOff>803741</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>84922</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -6015,112 +8237,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm rot="10800000" flipV="1">
-          <a:off x="18556942" y="7219704"/>
-          <a:ext cx="2417386" cy="1437717"/>
-        </a:xfrm>
-        <a:prstGeom prst="bentConnector3">
-          <a:avLst>
-            <a:gd name="adj1" fmla="val 50000"/>
-          </a:avLst>
-        </a:prstGeom>
-        <a:ln>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>159999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>25</xdr:col>
-      <xdr:colOff>803740</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>87707</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="101" name="カギ線コネクタ 100"/>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="27" idx="1"/>
-          <a:endCxn id="20" idx="3"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="10800000" flipV="1">
-          <a:off x="18566466" y="7219705"/>
-          <a:ext cx="2407862" cy="2617120"/>
-        </a:xfrm>
-        <a:prstGeom prst="bentConnector3">
-          <a:avLst>
-            <a:gd name="adj1" fmla="val 50000"/>
-          </a:avLst>
-        </a:prstGeom>
-        <a:ln>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>159999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>25</xdr:col>
-      <xdr:colOff>803741</xdr:colOff>
-      <xdr:row>65</xdr:row>
-      <xdr:rowOff>84012</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="107" name="カギ線コネクタ 106"/>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="27" idx="1"/>
-          <a:endCxn id="19" idx="3"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="10800000" flipV="1">
-          <a:off x="18556942" y="7219705"/>
-          <a:ext cx="2417387" cy="3790042"/>
+          <a:off x="18621377" y="9682758"/>
+          <a:ext cx="2422989" cy="1374964"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst>
@@ -6152,31 +8270,83 @@
     <xdr:from>
       <xdr:col>23</xdr:col>
       <xdr:colOff>9526</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>1421</xdr:rowOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>81557</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>803741</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>89388</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="101" name="カギ線コネクタ 100"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="27" idx="1"/>
+          <a:endCxn id="20" idx="3"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="10800000" flipV="1">
+          <a:off x="18630901" y="9682757"/>
+          <a:ext cx="2413465" cy="2579581"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 50000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>81557</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>25</xdr:col>
       <xdr:colOff>803740</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>159999</xdr:rowOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>84010</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="120" name="カギ線コネクタ 119"/>
+        <xdr:cNvPr id="107" name="カギ線コネクタ 106"/>
         <xdr:cNvCxnSpPr>
-          <a:stCxn id="15" idx="3"/>
-          <a:endCxn id="27" idx="1"/>
+          <a:stCxn id="27" idx="1"/>
+          <a:endCxn id="19" idx="3"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="18566467" y="4875980"/>
-          <a:ext cx="2407861" cy="2343725"/>
+        <a:xfrm rot="10800000" flipV="1">
+          <a:off x="18621375" y="9682757"/>
+          <a:ext cx="2422990" cy="3774353"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst>
-            <a:gd name="adj1" fmla="val 68150"/>
+            <a:gd name="adj1" fmla="val 50000"/>
           </a:avLst>
         </a:prstGeom>
         <a:ln>
@@ -6204,14 +8374,66 @@
     <xdr:from>
       <xdr:col>23</xdr:col>
       <xdr:colOff>9526</xdr:colOff>
-      <xdr:row>21</xdr:row>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>171190</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>803740</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>81558</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="120" name="カギ線コネクタ 119"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="15" idx="3"/>
+          <a:endCxn id="27" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="18630901" y="7200640"/>
+          <a:ext cx="2413464" cy="2482118"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 50000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>9526</xdr:colOff>
+      <xdr:row>34</xdr:row>
       <xdr:rowOff>1153</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>25</xdr:col>
       <xdr:colOff>803740</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>159999</xdr:rowOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>81558</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -6223,12 +8445,12 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="18566467" y="3531006"/>
-          <a:ext cx="2407861" cy="3688699"/>
+          <a:off x="18630901" y="5830453"/>
+          <a:ext cx="2413464" cy="3852305"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst>
-            <a:gd name="adj1" fmla="val 72804"/>
+            <a:gd name="adj1" fmla="val 50000"/>
           </a:avLst>
         </a:prstGeom>
         <a:ln>
@@ -6256,14 +8478,14 @@
     <xdr:from>
       <xdr:col>23</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>8381</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>25</xdr:col>
       <xdr:colOff>803740</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>159999</xdr:rowOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>81558</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -6275,12 +8497,12 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="18556941" y="2193528"/>
-          <a:ext cx="2417387" cy="5026177"/>
+          <a:off x="18621375" y="4466081"/>
+          <a:ext cx="2422990" cy="5216677"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst>
-            <a:gd name="adj1" fmla="val 81058"/>
+            <a:gd name="adj1" fmla="val 50000"/>
           </a:avLst>
         </a:prstGeom>
         <a:ln>
@@ -6308,13 +8530,13 @@
     <xdr:from>
       <xdr:col>17</xdr:col>
       <xdr:colOff>2183</xdr:colOff>
-      <xdr:row>69</xdr:row>
+      <xdr:row>82</xdr:row>
       <xdr:rowOff>166911</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>23</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>86</xdr:row>
+      <xdr:row>99</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -7217,6 +9439,82 @@
             <a:tabLst/>
             <a:defRPr/>
           </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>u1g_acfmdispif_igswsts</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>    </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>イグニッション状態公開値 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>OFF,ON[-]</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
           <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
             <a:solidFill>
               <a:schemeClr val="dk1"/>
@@ -7259,13 +9557,13 @@
     <xdr:from>
       <xdr:col>23</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>5601</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>25</xdr:col>
       <xdr:colOff>801221</xdr:colOff>
-      <xdr:row>77</xdr:row>
+      <xdr:row>90</xdr:row>
       <xdr:rowOff>167499</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -7283,7 +9581,7 @@
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst>
-            <a:gd name="adj1" fmla="val 91299"/>
+            <a:gd name="adj1" fmla="val 66705"/>
           </a:avLst>
         </a:prstGeom>
         <a:ln>
@@ -7311,13 +9609,13 @@
     <xdr:from>
       <xdr:col>23</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>35</xdr:row>
       <xdr:rowOff>90391</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>26</xdr:col>
       <xdr:colOff>8253</xdr:colOff>
-      <xdr:row>77</xdr:row>
+      <xdr:row>90</xdr:row>
       <xdr:rowOff>167499</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -7363,13 +9661,13 @@
     <xdr:from>
       <xdr:col>23</xdr:col>
       <xdr:colOff>1</xdr:colOff>
-      <xdr:row>32</xdr:row>
+      <xdr:row>45</xdr:row>
       <xdr:rowOff>102</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>26</xdr:col>
       <xdr:colOff>13325</xdr:colOff>
-      <xdr:row>77</xdr:row>
+      <xdr:row>90</xdr:row>
       <xdr:rowOff>167500</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -7414,15 +9712,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>23</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>159998</xdr:rowOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>81557</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>25</xdr:col>
-      <xdr:colOff>803741</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>167499</xdr:rowOff>
+      <xdr:colOff>803740</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>169180</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -7434,12 +9732,12 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm rot="10800000" flipV="1">
-          <a:off x="18556942" y="7219704"/>
-          <a:ext cx="2417387" cy="5890589"/>
+          <a:off x="18621375" y="9682757"/>
+          <a:ext cx="2422990" cy="5916923"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst>
-            <a:gd name="adj1" fmla="val 7353"/>
+            <a:gd name="adj1" fmla="val 50000"/>
           </a:avLst>
         </a:prstGeom>
         <a:ln>
@@ -7467,13 +9765,13 @@
     <xdr:from>
       <xdr:col>17</xdr:col>
       <xdr:colOff>2361</xdr:colOff>
-      <xdr:row>87</xdr:row>
+      <xdr:row>100</xdr:row>
       <xdr:rowOff>165603</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>23</xdr:col>
       <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>97</xdr:row>
+      <xdr:row>110</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -7535,41 +9833,6 @@
           </a:r>
         </a:p>
         <a:p>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
-              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>vdg_avehstsif_pwon()   </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
-              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>仮想マシン状態初期化処理</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
-            <a:solidFill>
-              <a:schemeClr val="dk1"/>
-            </a:solidFill>
-            <a:effectLst/>
-            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
-            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
-            <a:cs typeface="+mn-cs"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
           <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
             <a:lnSpc>
               <a:spcPct val="100000"/>
@@ -7588,40 +9851,40 @@
             <a:defRPr/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
-              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>vdg_avehstsif_64msm()  </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
-              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>仮想マシン状態定期処理</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
-              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t> </a:t>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>vdg_avehstsif_pwon()   </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>仮想マシン状態初期化処理 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>OFF,ON[-]</a:t>
           </a:r>
           <a:endParaRPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
             <a:solidFill>
@@ -7661,7 +9924,7 @@
               <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>vdg_avehstsif_stop     </a:t>
+            <a:t>vdg_avehstsif_64msm()  </a:t>
           </a:r>
           <a:r>
             <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0">
@@ -7673,7 +9936,31 @@
               <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>仮想マシン停止状態</a:t>
+            <a:t>仮想マシン状態定期処理</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>OFF,ON[-]</a:t>
           </a:r>
           <a:endParaRPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
             <a:solidFill>
@@ -7713,7 +10000,7 @@
               <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>vdg_avehstsif_run      </a:t>
+            <a:t>vdg_avehstsif_stop     </a:t>
           </a:r>
           <a:r>
             <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0">
@@ -7725,12 +10012,28 @@
               <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>仮想マシン走行状態</a:t>
-          </a:r>
-          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
+            <a:t>仮想マシン停止状態 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>OFF,ON[-]</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
             <a:effectLst/>
             <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
             <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:cs typeface="+mn-cs"/>
           </a:endParaRPr>
         </a:p>
         <a:p>
@@ -7761,7 +10064,7 @@
               <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>vdg_avehstsif_spdup     </a:t>
+            <a:t>vdg_avehstsif_run      </a:t>
           </a:r>
           <a:r>
             <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0">
@@ -7773,7 +10076,19 @@
               <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>仮想マシン加速状態</a:t>
+            <a:t>仮想マシン走行状態 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>OFF,ON[-]</a:t>
           </a:r>
           <a:endParaRPr lang="ja-JP" altLang="ja-JP">
             <a:effectLst/>
@@ -7809,7 +10124,7 @@
               <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>vdg_avehstsif_spddw     </a:t>
+            <a:t>vdg_avehstsif_spdup    </a:t>
           </a:r>
           <a:r>
             <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0">
@@ -7821,7 +10136,19 @@
               <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>仮想マシン減速状態</a:t>
+            <a:t>仮想マシン加速状態 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>OFF,ON[-]</a:t>
           </a:r>
           <a:endParaRPr lang="ja-JP" altLang="ja-JP">
             <a:effectLst/>
@@ -7857,7 +10184,7 @@
               <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>vdg_avehstsif_enst     </a:t>
+            <a:t>vdg_avehstsif_spddw    </a:t>
           </a:r>
           <a:r>
             <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0">
@@ -7869,7 +10196,19 @@
               <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>仮想マシンエンスト状態</a:t>
+            <a:t>仮想マシン減速状態 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>OFF,ON[-]</a:t>
           </a:r>
           <a:endParaRPr lang="ja-JP" altLang="ja-JP">
             <a:effectLst/>
@@ -7878,14 +10217,97 @@
           </a:endParaRPr>
         </a:p>
         <a:p>
-          <a:endParaRPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
-            <a:solidFill>
-              <a:schemeClr val="dk1"/>
-            </a:solidFill>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>vdg_avehstsif_enst     </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>仮想マシンエンスト状態</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>OFF,ON[-]</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
             <a:effectLst/>
-            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
-            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
-            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -7896,13 +10318,13 @@
     <xdr:from>
       <xdr:col>23</xdr:col>
       <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>55</xdr:row>
-      <xdr:rowOff>164976</xdr:rowOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>166656</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>26</xdr:col>
       <xdr:colOff>13728</xdr:colOff>
-      <xdr:row>92</xdr:row>
+      <xdr:row>105</xdr:row>
       <xdr:rowOff>82801</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -7915,8 +10337,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm rot="10800000" flipV="1">
-          <a:off x="18566466" y="9409829"/>
-          <a:ext cx="2424674" cy="6137090"/>
+          <a:off x="18630900" y="11996706"/>
+          <a:ext cx="2433078" cy="6088345"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst>
@@ -7942,6 +10364,1914 @@
         </a:fontRef>
       </xdr:style>
     </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>553</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>88299</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>2184</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>171903</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="98" name="カギ線コネクタ 97"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="147" idx="1"/>
+          <a:endCxn id="7" idx="3"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="10800000">
+          <a:off x="11430553" y="7164013"/>
+          <a:ext cx="2450917" cy="8928247"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 68027"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>553</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>88298</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>2362</xdr:colOff>
+      <xdr:row>105</xdr:row>
+      <xdr:rowOff>82802</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="100" name="カギ線コネクタ 99"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="174" idx="1"/>
+          <a:endCxn id="7" idx="3"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="10800000">
+          <a:off x="11430553" y="7164012"/>
+          <a:ext cx="2451095" cy="11492540"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 80565"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>806643</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>802595</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="103" name="テキスト ボックス 102"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13734367" y="1878724"/>
+          <a:ext cx="4843849" cy="1707931"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent4">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>sacaramngif.h</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>vdg_sacaramngif_pwon()      SAC</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>エリアマネージャー</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>pwon</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>vdg_sacaramngif_4msmin()    </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>SAC</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>エリアマネージャー</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>4ms</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>入力</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>vdg_sacaramngif_4msmout()   </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>SAC</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>エリアマネージャー</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>4ms</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>出力</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>vdg_sacaramngif_16msmin()   </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>SAC</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>エリアマネージャー</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>16ms</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>入力</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>vdg_sacaramngif_16msmout()  </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>SAC</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>エリアマネージャー</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>16ms</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>出力</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>vdg_sacaramngif_64msmin()   </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>SAC</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>エリアマネージャー</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>64ms</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>入力</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>vdg_sacaramngif_64msmout()  </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>SAC</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>エリアマネージャー</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>64ms</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>出力</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>807384</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>168085</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>801781</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="104" name="テキスト ボックス 103"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="21048009" y="1882585"/>
+          <a:ext cx="4852147" cy="1708340"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>aplaramngif.h</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>vdg_aplaramngif_pwon()      </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>APL</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>エリアマネージャー</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>pwon</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>vdg_aplaramngif_4msmin()    </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>APL</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>エリアマネージャー</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>4ms</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>入力</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>vdg_aplaramngif_4msmout()   </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>APL</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>エリアマネージャー</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>4ms</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>出力</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>vdg_aplaramngif_16msmin()   </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>APL</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>エリアマネージャー</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>16ms</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>入力</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>vdg_aplaramngif_16msmout()  </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>APL</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>エリアマネージャー</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>16ms</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>出力</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>vdg_aplaramngif_64msmin()   </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>APL</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>エリアマネージャー</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>64ms</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>入力</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>vdg_aplaramngif_64msmout()  </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>APL</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>エリアマネージャー</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>64ms</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>出力</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>11205</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>11206</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>41</xdr:col>
+      <xdr:colOff>320967</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>11206</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="105" name="テキスト ボックス 104"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="28250029" y="1860177"/>
+          <a:ext cx="5150703" cy="1680882"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFCCFF"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>simaramngif.h</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>vdg_simaramngif_pwon()         SIM</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>エリアマネージャー</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>pwon</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>vdg_simaramngif_4msmin()       SIM</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>エリアマネージャー</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>4ms</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>入力</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>vdg_simaramngif_4msmout()      SIM</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>エリアマネージャー</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>4ms</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>出力</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>vdg_simaramngif_16msmin()      SIM</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>エリアマネージャー</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>16ms</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>入力</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>vdg_simaramngif_16msmout()     SIM</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>エリアマネージャー</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>16ms</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>出力</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>vdg_simaramngif_64msmin()      SIM</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>エリアマネージャー</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>64ms</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>入力</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>vdg_simaramngif_64msmout()     SIM</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>エリアマネージャー</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>64ms</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>出力</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
+            <a:effectLst/>
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>380921</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>36099</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>745840</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>77561</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="79" name="テキスト ボックス 78"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13443778" y="212992"/>
+          <a:ext cx="6079919" cy="395248"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent4">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>APL</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -8234,13 +12564,846 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="F1:AS12"/>
+  <dimension ref="B2:Q50"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetData>
+    <row r="2" spans="2:17" x14ac:dyDescent="0.15">
+      <c r="B2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="3"/>
+    </row>
+    <row r="3" spans="2:17" x14ac:dyDescent="0.15">
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="2:17" x14ac:dyDescent="0.15">
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="4"/>
+      <c r="O4" s="4"/>
+      <c r="P4" s="4"/>
+      <c r="Q4" s="5"/>
+    </row>
+    <row r="5" spans="2:17" x14ac:dyDescent="0.15">
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
+      <c r="M5" s="4"/>
+      <c r="N5" s="4"/>
+      <c r="O5" s="4"/>
+      <c r="P5" s="4"/>
+      <c r="Q5" s="5"/>
+    </row>
+    <row r="6" spans="2:17" x14ac:dyDescent="0.15">
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="4"/>
+      <c r="M6" s="4"/>
+      <c r="N6" s="4"/>
+      <c r="O6" s="4"/>
+      <c r="P6" s="4"/>
+      <c r="Q6" s="5"/>
+    </row>
+    <row r="7" spans="2:17" x14ac:dyDescent="0.15">
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="4"/>
+      <c r="O7" s="4"/>
+      <c r="P7" s="4"/>
+      <c r="Q7" s="5"/>
+    </row>
+    <row r="8" spans="2:17" x14ac:dyDescent="0.15">
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="M8" s="4"/>
+      <c r="N8" s="4"/>
+      <c r="O8" s="4"/>
+      <c r="P8" s="4"/>
+      <c r="Q8" s="5"/>
+    </row>
+    <row r="9" spans="2:17" x14ac:dyDescent="0.15">
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
+      <c r="M9" s="4"/>
+      <c r="N9" s="4"/>
+      <c r="O9" s="4"/>
+      <c r="P9" s="4"/>
+      <c r="Q9" s="5"/>
+    </row>
+    <row r="10" spans="2:17" x14ac:dyDescent="0.15">
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="4"/>
+      <c r="L10" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="M10" s="4"/>
+      <c r="N10" s="4"/>
+      <c r="O10" s="4"/>
+      <c r="P10" s="4"/>
+      <c r="Q10" s="5"/>
+    </row>
+    <row r="11" spans="2:17" x14ac:dyDescent="0.15">
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="4"/>
+      <c r="L11" s="4"/>
+      <c r="M11" s="4"/>
+      <c r="N11" s="4"/>
+      <c r="O11" s="4"/>
+      <c r="P11" s="4"/>
+      <c r="Q11" s="5"/>
+    </row>
+    <row r="12" spans="2:17" x14ac:dyDescent="0.15">
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="K12" s="4"/>
+      <c r="L12" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="M12" s="4"/>
+      <c r="N12" s="4"/>
+      <c r="O12" s="4"/>
+      <c r="P12" s="4"/>
+      <c r="Q12" s="5"/>
+    </row>
+    <row r="13" spans="2:17" x14ac:dyDescent="0.15">
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="4"/>
+      <c r="L13" s="4"/>
+      <c r="M13" s="4"/>
+      <c r="N13" s="4"/>
+      <c r="O13" s="4"/>
+      <c r="P13" s="4"/>
+      <c r="Q13" s="5"/>
+    </row>
+    <row r="14" spans="2:17" x14ac:dyDescent="0.15">
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="K14" s="4"/>
+      <c r="L14" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="M14" s="4"/>
+      <c r="N14" s="4"/>
+      <c r="O14" s="4"/>
+      <c r="P14" s="4"/>
+      <c r="Q14" s="5"/>
+    </row>
+    <row r="15" spans="2:17" x14ac:dyDescent="0.15">
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="K15" s="4"/>
+      <c r="L15" s="4"/>
+      <c r="M15" s="4"/>
+      <c r="N15" s="4"/>
+      <c r="O15" s="4"/>
+      <c r="P15" s="4"/>
+      <c r="Q15" s="5"/>
+    </row>
+    <row r="16" spans="2:17" x14ac:dyDescent="0.15">
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="K16" s="4"/>
+      <c r="L16" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="M16" s="4"/>
+      <c r="N16" s="4"/>
+      <c r="O16" s="4"/>
+      <c r="P16" s="4"/>
+      <c r="Q16" s="5"/>
+    </row>
+    <row r="17" spans="4:17" x14ac:dyDescent="0.15">
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="K17" s="4"/>
+      <c r="L17" s="4"/>
+      <c r="M17" s="4"/>
+      <c r="N17" s="4"/>
+      <c r="O17" s="4"/>
+      <c r="P17" s="4"/>
+      <c r="Q17" s="5"/>
+    </row>
+    <row r="18" spans="4:17" x14ac:dyDescent="0.15">
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="K18" s="4"/>
+      <c r="L18" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="M18" s="4"/>
+      <c r="N18" s="4"/>
+      <c r="O18" s="4"/>
+      <c r="P18" s="4"/>
+      <c r="Q18" s="5"/>
+    </row>
+    <row r="19" spans="4:17" x14ac:dyDescent="0.15">
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+      <c r="K19" s="4"/>
+      <c r="L19" s="4"/>
+      <c r="M19" s="4"/>
+      <c r="N19" s="4"/>
+      <c r="O19" s="4"/>
+      <c r="P19" s="4"/>
+      <c r="Q19" s="5"/>
+    </row>
+    <row r="20" spans="4:17" x14ac:dyDescent="0.15">
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
+      <c r="K20" s="4"/>
+      <c r="L20" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="M20" s="4"/>
+      <c r="N20" s="4"/>
+      <c r="O20" s="4"/>
+      <c r="P20" s="4"/>
+      <c r="Q20" s="5"/>
+    </row>
+    <row r="21" spans="4:17" x14ac:dyDescent="0.15">
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="4"/>
+      <c r="K21" s="4"/>
+      <c r="L21" s="4"/>
+      <c r="M21" s="4"/>
+      <c r="N21" s="4"/>
+      <c r="O21" s="4"/>
+      <c r="P21" s="4"/>
+      <c r="Q21" s="5"/>
+    </row>
+    <row r="22" spans="4:17" x14ac:dyDescent="0.15">
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
+      <c r="K22" s="4"/>
+      <c r="L22" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="M22" s="4"/>
+      <c r="N22" s="4"/>
+      <c r="O22" s="4"/>
+      <c r="P22" s="4"/>
+      <c r="Q22" s="5"/>
+    </row>
+    <row r="23" spans="4:17" x14ac:dyDescent="0.15">
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="4"/>
+      <c r="K23" s="4"/>
+      <c r="L23" s="4"/>
+      <c r="M23" s="4"/>
+      <c r="N23" s="4"/>
+      <c r="O23" s="4"/>
+      <c r="P23" s="4"/>
+      <c r="Q23" s="5"/>
+    </row>
+    <row r="24" spans="4:17" x14ac:dyDescent="0.15">
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="4"/>
+      <c r="K24" s="4"/>
+      <c r="L24" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="M24" s="4"/>
+      <c r="N24" s="4"/>
+      <c r="O24" s="4"/>
+      <c r="P24" s="4"/>
+      <c r="Q24" s="5"/>
+    </row>
+    <row r="25" spans="4:17" x14ac:dyDescent="0.15">
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
+      <c r="K25" s="4"/>
+      <c r="L25" s="4"/>
+      <c r="M25" s="4"/>
+      <c r="N25" s="4"/>
+      <c r="O25" s="4"/>
+      <c r="P25" s="4"/>
+      <c r="Q25" s="5"/>
+    </row>
+    <row r="26" spans="4:17" x14ac:dyDescent="0.15">
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
+      <c r="K26" s="4"/>
+      <c r="L26" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M26" s="4"/>
+      <c r="N26" s="4"/>
+      <c r="O26" s="4"/>
+      <c r="P26" s="4"/>
+      <c r="Q26" s="5"/>
+    </row>
+    <row r="27" spans="4:17" x14ac:dyDescent="0.15">
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
+      <c r="K27" s="4"/>
+      <c r="L27" s="4"/>
+      <c r="M27" s="4"/>
+      <c r="N27" s="4"/>
+      <c r="O27" s="4"/>
+      <c r="P27" s="4"/>
+      <c r="Q27" s="5"/>
+    </row>
+    <row r="28" spans="4:17" x14ac:dyDescent="0.15">
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
+      <c r="K28" s="4"/>
+      <c r="L28" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="M28" s="4"/>
+      <c r="N28" s="4"/>
+      <c r="O28" s="4"/>
+      <c r="P28" s="4"/>
+      <c r="Q28" s="5"/>
+    </row>
+    <row r="29" spans="4:17" x14ac:dyDescent="0.15">
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
+      <c r="K29" s="4"/>
+      <c r="L29" s="4"/>
+      <c r="M29" s="4"/>
+      <c r="N29" s="4"/>
+      <c r="O29" s="4"/>
+      <c r="P29" s="4"/>
+      <c r="Q29" s="5"/>
+    </row>
+    <row r="30" spans="4:17" x14ac:dyDescent="0.15">
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
+      <c r="K30" s="4"/>
+      <c r="L30" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="M30" s="4"/>
+      <c r="N30" s="4"/>
+      <c r="O30" s="4"/>
+      <c r="P30" s="4"/>
+      <c r="Q30" s="5"/>
+    </row>
+    <row r="31" spans="4:17" x14ac:dyDescent="0.15">
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="4"/>
+      <c r="K31" s="4"/>
+      <c r="L31" s="4"/>
+      <c r="M31" s="4"/>
+      <c r="N31" s="4"/>
+      <c r="O31" s="4"/>
+      <c r="P31" s="4"/>
+      <c r="Q31" s="5"/>
+    </row>
+    <row r="32" spans="4:17" x14ac:dyDescent="0.15">
+      <c r="D32" s="4"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="4"/>
+      <c r="K32" s="4"/>
+      <c r="L32" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="M32" s="4"/>
+      <c r="N32" s="4"/>
+      <c r="O32" s="4"/>
+      <c r="P32" s="4"/>
+      <c r="Q32" s="5"/>
+    </row>
+    <row r="33" spans="4:17" x14ac:dyDescent="0.15">
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
+      <c r="K33" s="4"/>
+      <c r="L33" s="4"/>
+      <c r="M33" s="4"/>
+      <c r="N33" s="4"/>
+      <c r="O33" s="4"/>
+      <c r="P33" s="4"/>
+      <c r="Q33" s="5"/>
+    </row>
+    <row r="34" spans="4:17" x14ac:dyDescent="0.15">
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
+      <c r="I34" s="4"/>
+      <c r="J34" s="4"/>
+      <c r="K34" s="4"/>
+      <c r="L34" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="M34" s="4"/>
+      <c r="N34" s="4"/>
+      <c r="O34" s="4"/>
+      <c r="P34" s="4"/>
+      <c r="Q34" s="5"/>
+    </row>
+    <row r="35" spans="4:17" x14ac:dyDescent="0.15">
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
+      <c r="I35" s="4"/>
+      <c r="J35" s="4"/>
+      <c r="K35" s="4"/>
+      <c r="L35" s="4"/>
+      <c r="M35" s="4"/>
+      <c r="N35" s="4"/>
+      <c r="O35" s="4"/>
+      <c r="P35" s="4"/>
+      <c r="Q35" s="5"/>
+    </row>
+    <row r="36" spans="4:17" x14ac:dyDescent="0.15">
+      <c r="D36" s="4"/>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4"/>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4"/>
+      <c r="I36" s="4"/>
+      <c r="J36" s="4"/>
+      <c r="K36" s="4"/>
+      <c r="L36" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="M36" s="4"/>
+      <c r="N36" s="4"/>
+      <c r="O36" s="4"/>
+      <c r="P36" s="4"/>
+      <c r="Q36" s="5"/>
+    </row>
+    <row r="37" spans="4:17" x14ac:dyDescent="0.15">
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
+      <c r="I37" s="4"/>
+      <c r="J37" s="4"/>
+      <c r="K37" s="4"/>
+      <c r="L37" s="4"/>
+      <c r="M37" s="4"/>
+      <c r="N37" s="4"/>
+      <c r="O37" s="4"/>
+      <c r="P37" s="4"/>
+      <c r="Q37" s="5"/>
+    </row>
+    <row r="38" spans="4:17" x14ac:dyDescent="0.15">
+      <c r="D38" s="4"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
+      <c r="K38" s="4"/>
+      <c r="L38" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="M38" s="4"/>
+      <c r="N38" s="4"/>
+      <c r="O38" s="4"/>
+      <c r="P38" s="4"/>
+      <c r="Q38" s="5"/>
+    </row>
+    <row r="39" spans="4:17" x14ac:dyDescent="0.15">
+      <c r="D39" s="4"/>
+      <c r="E39" s="4"/>
+      <c r="F39" s="4"/>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
+      <c r="I39" s="4"/>
+      <c r="J39" s="4"/>
+      <c r="K39" s="4"/>
+      <c r="L39" s="4"/>
+      <c r="M39" s="4"/>
+      <c r="N39" s="4"/>
+      <c r="O39" s="4"/>
+      <c r="P39" s="4"/>
+      <c r="Q39" s="5"/>
+    </row>
+    <row r="40" spans="4:17" x14ac:dyDescent="0.15">
+      <c r="D40" s="4"/>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4"/>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
+      <c r="K40" s="4"/>
+      <c r="L40" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="M40" s="4"/>
+      <c r="N40" s="4"/>
+      <c r="O40" s="4"/>
+      <c r="P40" s="4"/>
+      <c r="Q40" s="5"/>
+    </row>
+    <row r="41" spans="4:17" x14ac:dyDescent="0.15">
+      <c r="D41" s="4"/>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4"/>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
+      <c r="K41" s="4"/>
+      <c r="L41" s="4"/>
+      <c r="M41" s="4"/>
+      <c r="N41" s="4"/>
+      <c r="O41" s="4"/>
+      <c r="P41" s="4"/>
+      <c r="Q41" s="5"/>
+    </row>
+    <row r="42" spans="4:17" x14ac:dyDescent="0.15">
+      <c r="D42" s="4"/>
+      <c r="E42" s="4"/>
+      <c r="F42" s="4"/>
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
+      <c r="I42" s="4"/>
+      <c r="J42" s="4"/>
+      <c r="K42" s="4"/>
+      <c r="L42" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="M42" s="4"/>
+      <c r="N42" s="4"/>
+      <c r="O42" s="4"/>
+      <c r="P42" s="4"/>
+      <c r="Q42" s="5"/>
+    </row>
+    <row r="43" spans="4:17" x14ac:dyDescent="0.15">
+      <c r="D43" s="4"/>
+      <c r="E43" s="4"/>
+      <c r="F43" s="4"/>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4"/>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4"/>
+      <c r="K43" s="4"/>
+      <c r="L43" s="4"/>
+      <c r="M43" s="4"/>
+      <c r="N43" s="4"/>
+      <c r="O43" s="4"/>
+      <c r="P43" s="4"/>
+      <c r="Q43" s="5"/>
+    </row>
+    <row r="44" spans="4:17" x14ac:dyDescent="0.15">
+      <c r="D44" s="4"/>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4"/>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="4"/>
+      <c r="K44" s="4"/>
+      <c r="L44" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="M44" s="4"/>
+      <c r="N44" s="4"/>
+      <c r="O44" s="4"/>
+      <c r="P44" s="4"/>
+      <c r="Q44" s="5"/>
+    </row>
+    <row r="45" spans="4:17" x14ac:dyDescent="0.15">
+      <c r="D45" s="4"/>
+      <c r="E45" s="4"/>
+      <c r="F45" s="4"/>
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
+      <c r="I45" s="4"/>
+      <c r="J45" s="4"/>
+      <c r="K45" s="4"/>
+      <c r="L45" s="4"/>
+      <c r="M45" s="4"/>
+      <c r="N45" s="4"/>
+      <c r="O45" s="4"/>
+      <c r="P45" s="4"/>
+      <c r="Q45" s="5"/>
+    </row>
+    <row r="46" spans="4:17" x14ac:dyDescent="0.15">
+      <c r="D46" s="4"/>
+      <c r="E46" s="4"/>
+      <c r="F46" s="4"/>
+      <c r="G46" s="4"/>
+      <c r="H46" s="4"/>
+      <c r="I46" s="4"/>
+      <c r="J46" s="4"/>
+      <c r="K46" s="4"/>
+      <c r="L46" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="M46" s="4"/>
+      <c r="N46" s="4"/>
+      <c r="O46" s="4"/>
+      <c r="P46" s="4"/>
+      <c r="Q46" s="5"/>
+    </row>
+    <row r="47" spans="4:17" x14ac:dyDescent="0.15">
+      <c r="D47" s="4"/>
+      <c r="E47" s="4"/>
+      <c r="F47" s="4"/>
+      <c r="G47" s="4"/>
+      <c r="H47" s="4"/>
+      <c r="I47" s="4"/>
+      <c r="J47" s="4"/>
+      <c r="K47" s="4"/>
+      <c r="L47" s="4"/>
+      <c r="M47" s="4"/>
+      <c r="N47" s="4"/>
+      <c r="O47" s="4"/>
+      <c r="P47" s="4"/>
+      <c r="Q47" s="5"/>
+    </row>
+    <row r="48" spans="4:17" x14ac:dyDescent="0.15">
+      <c r="D48" s="4"/>
+      <c r="E48" s="4"/>
+      <c r="F48" s="4"/>
+      <c r="G48" s="4"/>
+      <c r="H48" s="4"/>
+      <c r="I48" s="4"/>
+      <c r="J48" s="4"/>
+      <c r="K48" s="4"/>
+      <c r="L48" s="4"/>
+      <c r="M48" s="4"/>
+      <c r="N48" s="4"/>
+      <c r="O48" s="4"/>
+      <c r="P48" s="4"/>
+      <c r="Q48" s="5"/>
+    </row>
+    <row r="49" spans="4:17" x14ac:dyDescent="0.15">
+      <c r="D49" s="4"/>
+      <c r="E49" s="4"/>
+      <c r="F49" s="4"/>
+      <c r="G49" s="4"/>
+      <c r="H49" s="4"/>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4"/>
+      <c r="K49" s="4"/>
+      <c r="L49" s="4"/>
+      <c r="M49" s="4"/>
+      <c r="N49" s="4"/>
+      <c r="O49" s="4"/>
+      <c r="P49" s="4"/>
+      <c r="Q49" s="5"/>
+    </row>
+    <row r="50" spans="4:17" x14ac:dyDescent="0.15">
+      <c r="D50" s="4"/>
+      <c r="E50" s="4"/>
+      <c r="F50" s="4"/>
+      <c r="G50" s="4"/>
+      <c r="H50" s="4"/>
+      <c r="I50" s="4"/>
+      <c r="J50" s="4"/>
+      <c r="K50" s="4"/>
+      <c r="L50" s="4"/>
+      <c r="M50" s="4"/>
+      <c r="N50" s="4"/>
+      <c r="O50" s="4"/>
+      <c r="P50" s="4"/>
+      <c r="Q50" s="5"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="F1:AS25"/>
   <sheetFormatPr defaultColWidth="10.625" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="16384" width="10.625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="6:45" x14ac:dyDescent="0.15">
+    <row r="1" spans="6:10" x14ac:dyDescent="0.15">
       <c r="F1" s="2" t="s">
         <v>1</v>
       </c>
@@ -8249,20 +13412,20 @@
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
     </row>
-    <row r="2" spans="6:45" x14ac:dyDescent="0.15">
+    <row r="2" spans="6:10" x14ac:dyDescent="0.15">
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
     </row>
-    <row r="10" spans="6:45" x14ac:dyDescent="0.15">
-      <c r="H10" s="1" t="s">
+    <row r="23" spans="8:45" x14ac:dyDescent="0.15">
+      <c r="H23" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="6:45" x14ac:dyDescent="0.15">
-      <c r="AS12" s="1" t="s">
+    <row r="25" spans="8:45" x14ac:dyDescent="0.15">
+      <c r="AS25" s="1" t="s">
         <v>2</v>
       </c>
     </row>
